--- a/Sets-vervestacks.xlsx
+++ b/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VS_CEA_8C\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BC8B4B-54C5-4E7E-8E55-9B010AE6EA68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A064BF99-4831-4F98-8C34-4FAE6948E688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12772" firstSheet="3" activeTab="9" xr2:uid="{E722805A-B1BC-41F1-9AF9-C4385EA1BFAD}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12772" firstSheet="3" activeTab="9" xr2:uid="{676BC4E6-DB58-4E82-B1BF-6D01B39DCC46}"/>
   </bookViews>
   <sheets>
     <sheet name="geo_sets_FRA" sheetId="2" r:id="rId1"/>
@@ -3907,7 +3907,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Heading 2 2" xfId="2" xr:uid="{EE788458-9F4F-4578-9844-8875B6D746A4}"/>
+    <cellStyle name="Heading 2 2" xfId="2" xr:uid="{51DAE24B-C749-47A7-B20F-C66D4369708E}"/>
     <cellStyle name="Heading 3" xfId="1" builtinId="18"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -4220,7 +4220,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33244D52-67C8-406C-A2F7-A4D2D594DDB7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC31B416-13A1-4EA0-8543-4DE947C7B39B}">
   <dimension ref="B9:E119"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5775,7 +5775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A919A1F-31A4-4517-A0AB-6357111738EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{136D46E6-4B66-4429-BA15-1B4CA0197E78}">
   <dimension ref="A1:K34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -6192,7 +6192,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{678B3DBA-0F33-4C22-94A8-216A622D33AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EECBF0D2-466A-4BF2-B988-FE3506C81201}">
   <dimension ref="B9:E101"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7495,7 +7495,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96C4025F-07D3-4E00-8002-DFCE0171B34E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4072C07F-24E6-4B90-B963-299622792739}">
   <dimension ref="B9:E41"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7958,7 +7958,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A35467-B9C6-46D3-9286-5321EB655806}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{002ECF52-D0F6-4C35-BEC0-E6CFCFE890BF}">
   <dimension ref="B9:E102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9275,7 +9275,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8937686B-BE3D-49B0-999E-9EACBD44905B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6B24935-0419-4114-8AA6-5A7F5DD2B3B1}">
   <dimension ref="B9:E49"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9850,7 +9850,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD615D9-6D88-44EC-B813-9635009B9215}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0450009B-38FA-4B4A-B923-CD0813EF619B}">
   <dimension ref="B9:E98"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11111,7 +11111,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EB4A933-7E18-4880-AB83-91CB2D46471C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{410B152E-A4C3-47A2-AF79-6380E988887E}">
   <dimension ref="B9:E97"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12358,7 +12358,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0E2437E-4C24-4AFA-93BE-B872C5BCA1DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E14F65-9E8E-4A6E-9013-CF9F095B5772}">
   <dimension ref="B9:E48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12919,7 +12919,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74780ADE-0332-4793-AF56-368FA8423D22}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92AF78F1-D388-4A5F-B49D-2FB1EF9C24E2}">
   <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>

--- a/Sets-vervestacks.xlsx
+++ b/Sets-vervestacks.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VS_CEA_8C\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A064BF99-4831-4F98-8C34-4FAE6948E688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D2E2D3-7406-431F-AC01-D49B3D0DC1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12772" firstSheet="3" activeTab="9" xr2:uid="{676BC4E6-DB58-4E82-B1BF-6D01B39DCC46}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12772" firstSheet="3" activeTab="9" xr2:uid="{38D5EBEC-5899-4D36-BF2C-8D68986B9C4B}"/>
   </bookViews>
   <sheets>
     <sheet name="geo_sets_FRA" sheetId="2" r:id="rId1"/>
     <sheet name="geo_sets_GBR" sheetId="3" r:id="rId2"/>
-    <sheet name="geo_sets_BEL" sheetId="4" r:id="rId3"/>
-    <sheet name="geo_sets_DEU" sheetId="5" r:id="rId4"/>
-    <sheet name="geo_sets_CHE" sheetId="6" r:id="rId5"/>
-    <sheet name="geo_sets_ITA" sheetId="7" r:id="rId6"/>
-    <sheet name="geo_sets_ESP" sheetId="8" r:id="rId7"/>
-    <sheet name="geo_sets_NLD" sheetId="9" r:id="rId8"/>
+    <sheet name="geo_sets_NLD" sheetId="4" r:id="rId3"/>
+    <sheet name="geo_sets_BEL" sheetId="5" r:id="rId4"/>
+    <sheet name="geo_sets_DEU" sheetId="6" r:id="rId5"/>
+    <sheet name="geo_sets_CHE" sheetId="7" r:id="rId6"/>
+    <sheet name="geo_sets_ITA" sheetId="8" r:id="rId7"/>
+    <sheet name="geo_sets_ESP" sheetId="9" r:id="rId8"/>
     <sheet name="VEDA_Sets-Comm" sheetId="10" r:id="rId9"/>
     <sheet name="VEDA_Sets-Proc" sheetId="11" r:id="rId10"/>
   </sheets>
@@ -1265,6 +1265,234 @@
     <t>elc_wof_GBR_034</t>
   </si>
   <si>
+    <t>p_Leeuwarden_NLD</t>
+  </si>
+  <si>
+    <t>*[_]Leeuwarden_NLD</t>
+  </si>
+  <si>
+    <t>p_Veendam_NLD</t>
+  </si>
+  <si>
+    <t>*[_]Veendam_NLD</t>
+  </si>
+  <si>
+    <t>p_Maastricht_NLD</t>
+  </si>
+  <si>
+    <t>*[_]Maastricht_NLD</t>
+  </si>
+  <si>
+    <t>p_Eindhoven_NLD</t>
+  </si>
+  <si>
+    <t>*[_]Eindhoven_NLD</t>
+  </si>
+  <si>
+    <t>p_Hoogezand_NLD</t>
+  </si>
+  <si>
+    <t>*[_]Hoogezand_NLD</t>
+  </si>
+  <si>
+    <t>p_Tilburg_NLD</t>
+  </si>
+  <si>
+    <t>*[_]Tilburg_NLD</t>
+  </si>
+  <si>
+    <t>p_Amsterdam_NLD</t>
+  </si>
+  <si>
+    <t>*[_]Amsterdam_NLD</t>
+  </si>
+  <si>
+    <t>p_Roosendaal_NLD</t>
+  </si>
+  <si>
+    <t>*[_]Roosendaal_NLD</t>
+  </si>
+  <si>
+    <t>p_Groningen_NLD</t>
+  </si>
+  <si>
+    <t>*[_]Groningen_NLD</t>
+  </si>
+  <si>
+    <t>p_Nijmegen_NLD</t>
+  </si>
+  <si>
+    <t>*[_]Nijmegen_NLD</t>
+  </si>
+  <si>
+    <t>p_Enschede_NLD</t>
+  </si>
+  <si>
+    <t>*[_]Enschede_NLD</t>
+  </si>
+  <si>
+    <t>p_Apeldoorn_NLD</t>
+  </si>
+  <si>
+    <t>*[_]Apeldoorn_NLD</t>
+  </si>
+  <si>
+    <t>p_Rotterdam_NLD</t>
+  </si>
+  <si>
+    <t>*[_]Rotterdam_NLD</t>
+  </si>
+  <si>
+    <t>rez_spv_NLD_001</t>
+  </si>
+  <si>
+    <t>elc_spv_NLD_001</t>
+  </si>
+  <si>
+    <t>rez_spv_NLD_002</t>
+  </si>
+  <si>
+    <t>elc_spv_NLD_002</t>
+  </si>
+  <si>
+    <t>rez_spv_NLD_003</t>
+  </si>
+  <si>
+    <t>elc_spv_NLD_003</t>
+  </si>
+  <si>
+    <t>rez_spv_NLD_004</t>
+  </si>
+  <si>
+    <t>elc_spv_NLD_004</t>
+  </si>
+  <si>
+    <t>rez_spv_NLD_005</t>
+  </si>
+  <si>
+    <t>elc_spv_NLD_005</t>
+  </si>
+  <si>
+    <t>rez_spv_NLD_006</t>
+  </si>
+  <si>
+    <t>elc_spv_NLD_006</t>
+  </si>
+  <si>
+    <t>rez_spv_NLD_007</t>
+  </si>
+  <si>
+    <t>elc_spv_NLD_007</t>
+  </si>
+  <si>
+    <t>rez_spv_NLD_008</t>
+  </si>
+  <si>
+    <t>elc_spv_NLD_008</t>
+  </si>
+  <si>
+    <t>rez_spv_NLD_009</t>
+  </si>
+  <si>
+    <t>elc_spv_NLD_009</t>
+  </si>
+  <si>
+    <t>rez_spv_NLD_010</t>
+  </si>
+  <si>
+    <t>elc_spv_NLD_010</t>
+  </si>
+  <si>
+    <t>rez_won_NLD_001</t>
+  </si>
+  <si>
+    <t>elc_won_NLD_001</t>
+  </si>
+  <si>
+    <t>rez_won_NLD_002</t>
+  </si>
+  <si>
+    <t>elc_won_NLD_002</t>
+  </si>
+  <si>
+    <t>rez_won_NLD_003</t>
+  </si>
+  <si>
+    <t>elc_won_NLD_003</t>
+  </si>
+  <si>
+    <t>rez_won_NLD_004</t>
+  </si>
+  <si>
+    <t>elc_won_NLD_004</t>
+  </si>
+  <si>
+    <t>rez_won_NLD_005</t>
+  </si>
+  <si>
+    <t>elc_won_NLD_005</t>
+  </si>
+  <si>
+    <t>rez_won_NLD_006</t>
+  </si>
+  <si>
+    <t>elc_won_NLD_006</t>
+  </si>
+  <si>
+    <t>rez_won_NLD_007</t>
+  </si>
+  <si>
+    <t>elc_won_NLD_007</t>
+  </si>
+  <si>
+    <t>rez_won_NLD_008</t>
+  </si>
+  <si>
+    <t>elc_won_NLD_008</t>
+  </si>
+  <si>
+    <t>rez_won_NLD_009</t>
+  </si>
+  <si>
+    <t>elc_won_NLD_009</t>
+  </si>
+  <si>
+    <t>rez_won_NLD_010</t>
+  </si>
+  <si>
+    <t>elc_won_NLD_010</t>
+  </si>
+  <si>
+    <t>rez_wof_NLD_001</t>
+  </si>
+  <si>
+    <t>elc_wof_NLD_001</t>
+  </si>
+  <si>
+    <t>rez_wof_NLD_002</t>
+  </si>
+  <si>
+    <t>elc_wof_NLD_002</t>
+  </si>
+  <si>
+    <t>rez_wof_NLD_003</t>
+  </si>
+  <si>
+    <t>elc_wof_NLD_003</t>
+  </si>
+  <si>
+    <t>rez_wof_NLD_004</t>
+  </si>
+  <si>
+    <t>elc_wof_NLD_004</t>
+  </si>
+  <si>
+    <t>rez_wof_NLD_005</t>
+  </si>
+  <si>
+    <t>elc_wof_NLD_005</t>
+  </si>
+  <si>
     <t>p_Charleroi_BEL</t>
   </si>
   <si>
@@ -3285,234 +3513,6 @@
   </si>
   <si>
     <t>elc_wof_ESP_019</t>
-  </si>
-  <si>
-    <t>p_Leeuwarden_NLD</t>
-  </si>
-  <si>
-    <t>*[_]Leeuwarden_NLD</t>
-  </si>
-  <si>
-    <t>p_Veendam_NLD</t>
-  </si>
-  <si>
-    <t>*[_]Veendam_NLD</t>
-  </si>
-  <si>
-    <t>p_Maastricht_NLD</t>
-  </si>
-  <si>
-    <t>*[_]Maastricht_NLD</t>
-  </si>
-  <si>
-    <t>p_Eindhoven_NLD</t>
-  </si>
-  <si>
-    <t>*[_]Eindhoven_NLD</t>
-  </si>
-  <si>
-    <t>p_Hoogezand_NLD</t>
-  </si>
-  <si>
-    <t>*[_]Hoogezand_NLD</t>
-  </si>
-  <si>
-    <t>p_Tilburg_NLD</t>
-  </si>
-  <si>
-    <t>*[_]Tilburg_NLD</t>
-  </si>
-  <si>
-    <t>p_Amsterdam_NLD</t>
-  </si>
-  <si>
-    <t>*[_]Amsterdam_NLD</t>
-  </si>
-  <si>
-    <t>p_Roosendaal_NLD</t>
-  </si>
-  <si>
-    <t>*[_]Roosendaal_NLD</t>
-  </si>
-  <si>
-    <t>p_Groningen_NLD</t>
-  </si>
-  <si>
-    <t>*[_]Groningen_NLD</t>
-  </si>
-  <si>
-    <t>p_Nijmegen_NLD</t>
-  </si>
-  <si>
-    <t>*[_]Nijmegen_NLD</t>
-  </si>
-  <si>
-    <t>p_Enschede_NLD</t>
-  </si>
-  <si>
-    <t>*[_]Enschede_NLD</t>
-  </si>
-  <si>
-    <t>p_Apeldoorn_NLD</t>
-  </si>
-  <si>
-    <t>*[_]Apeldoorn_NLD</t>
-  </si>
-  <si>
-    <t>p_Rotterdam_NLD</t>
-  </si>
-  <si>
-    <t>*[_]Rotterdam_NLD</t>
-  </si>
-  <si>
-    <t>rez_spv_NLD_001</t>
-  </si>
-  <si>
-    <t>elc_spv_NLD_001</t>
-  </si>
-  <si>
-    <t>rez_spv_NLD_002</t>
-  </si>
-  <si>
-    <t>elc_spv_NLD_002</t>
-  </si>
-  <si>
-    <t>rez_spv_NLD_003</t>
-  </si>
-  <si>
-    <t>elc_spv_NLD_003</t>
-  </si>
-  <si>
-    <t>rez_spv_NLD_004</t>
-  </si>
-  <si>
-    <t>elc_spv_NLD_004</t>
-  </si>
-  <si>
-    <t>rez_spv_NLD_005</t>
-  </si>
-  <si>
-    <t>elc_spv_NLD_005</t>
-  </si>
-  <si>
-    <t>rez_spv_NLD_006</t>
-  </si>
-  <si>
-    <t>elc_spv_NLD_006</t>
-  </si>
-  <si>
-    <t>rez_spv_NLD_007</t>
-  </si>
-  <si>
-    <t>elc_spv_NLD_007</t>
-  </si>
-  <si>
-    <t>rez_spv_NLD_008</t>
-  </si>
-  <si>
-    <t>elc_spv_NLD_008</t>
-  </si>
-  <si>
-    <t>rez_spv_NLD_009</t>
-  </si>
-  <si>
-    <t>elc_spv_NLD_009</t>
-  </si>
-  <si>
-    <t>rez_spv_NLD_010</t>
-  </si>
-  <si>
-    <t>elc_spv_NLD_010</t>
-  </si>
-  <si>
-    <t>rez_won_NLD_001</t>
-  </si>
-  <si>
-    <t>elc_won_NLD_001</t>
-  </si>
-  <si>
-    <t>rez_won_NLD_002</t>
-  </si>
-  <si>
-    <t>elc_won_NLD_002</t>
-  </si>
-  <si>
-    <t>rez_won_NLD_003</t>
-  </si>
-  <si>
-    <t>elc_won_NLD_003</t>
-  </si>
-  <si>
-    <t>rez_won_NLD_004</t>
-  </si>
-  <si>
-    <t>elc_won_NLD_004</t>
-  </si>
-  <si>
-    <t>rez_won_NLD_005</t>
-  </si>
-  <si>
-    <t>elc_won_NLD_005</t>
-  </si>
-  <si>
-    <t>rez_won_NLD_006</t>
-  </si>
-  <si>
-    <t>elc_won_NLD_006</t>
-  </si>
-  <si>
-    <t>rez_won_NLD_007</t>
-  </si>
-  <si>
-    <t>elc_won_NLD_007</t>
-  </si>
-  <si>
-    <t>rez_won_NLD_008</t>
-  </si>
-  <si>
-    <t>elc_won_NLD_008</t>
-  </si>
-  <si>
-    <t>rez_won_NLD_009</t>
-  </si>
-  <si>
-    <t>elc_won_NLD_009</t>
-  </si>
-  <si>
-    <t>rez_won_NLD_010</t>
-  </si>
-  <si>
-    <t>elc_won_NLD_010</t>
-  </si>
-  <si>
-    <t>rez_wof_NLD_001</t>
-  </si>
-  <si>
-    <t>elc_wof_NLD_001</t>
-  </si>
-  <si>
-    <t>rez_wof_NLD_002</t>
-  </si>
-  <si>
-    <t>elc_wof_NLD_002</t>
-  </si>
-  <si>
-    <t>rez_wof_NLD_003</t>
-  </si>
-  <si>
-    <t>elc_wof_NLD_003</t>
-  </si>
-  <si>
-    <t>rez_wof_NLD_004</t>
-  </si>
-  <si>
-    <t>elc_wof_NLD_004</t>
-  </si>
-  <si>
-    <t>rez_wof_NLD_005</t>
-  </si>
-  <si>
-    <t>elc_wof_NLD_005</t>
   </si>
   <si>
     <t>~TFM_Csets</t>
@@ -3907,7 +3907,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Heading 2 2" xfId="2" xr:uid="{51DAE24B-C749-47A7-B20F-C66D4369708E}"/>
+    <cellStyle name="Heading 2 2" xfId="2" xr:uid="{732082A1-926D-415E-BFB2-F0B0870A393B}"/>
     <cellStyle name="Heading 3" xfId="1" builtinId="18"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -4220,7 +4220,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC31B416-13A1-4EA0-8543-4DE947C7B39B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{433002D6-4243-4D2A-A5E9-D49BE280F78B}">
   <dimension ref="B9:E119"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5775,7 +5775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{136D46E6-4B66-4429-BA15-1B4CA0197E78}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C02C4663-E7F7-4F75-ACB6-800D830CFB0B}">
   <dimension ref="A1:K34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -6192,7 +6192,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EECBF0D2-466A-4BF2-B988-FE3506C81201}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87FE94BB-DDAA-4BC2-9BD6-3EDD296D6B00}">
   <dimension ref="B9:E101"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7495,7 +7495,568 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4072C07F-24E6-4B90-B963-299622792739}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAAB14EE-92AC-4995-985F-A8F3583C3637}">
+  <dimension ref="B9:E48"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>406</v>
+      </c>
+      <c r="C11" t="s">
+        <v>407</v>
+      </c>
+      <c r="D11" t="s">
+        <v>407</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>408</v>
+      </c>
+      <c r="C12" t="s">
+        <v>409</v>
+      </c>
+      <c r="D12" t="s">
+        <v>409</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
+        <v>410</v>
+      </c>
+      <c r="C13" t="s">
+        <v>411</v>
+      </c>
+      <c r="D13" t="s">
+        <v>411</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>412</v>
+      </c>
+      <c r="C14" t="s">
+        <v>413</v>
+      </c>
+      <c r="D14" t="s">
+        <v>413</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>414</v>
+      </c>
+      <c r="C15" t="s">
+        <v>415</v>
+      </c>
+      <c r="D15" t="s">
+        <v>415</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>416</v>
+      </c>
+      <c r="C16" t="s">
+        <v>417</v>
+      </c>
+      <c r="D16" t="s">
+        <v>417</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>418</v>
+      </c>
+      <c r="C17" t="s">
+        <v>419</v>
+      </c>
+      <c r="D17" t="s">
+        <v>419</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
+        <v>420</v>
+      </c>
+      <c r="C18" t="s">
+        <v>421</v>
+      </c>
+      <c r="D18" t="s">
+        <v>421</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>422</v>
+      </c>
+      <c r="C19" t="s">
+        <v>423</v>
+      </c>
+      <c r="D19" t="s">
+        <v>423</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B20" t="s">
+        <v>424</v>
+      </c>
+      <c r="C20" t="s">
+        <v>425</v>
+      </c>
+      <c r="D20" t="s">
+        <v>425</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>426</v>
+      </c>
+      <c r="C21" t="s">
+        <v>427</v>
+      </c>
+      <c r="D21" t="s">
+        <v>427</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>428</v>
+      </c>
+      <c r="C22" t="s">
+        <v>429</v>
+      </c>
+      <c r="D22" t="s">
+        <v>429</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B23" t="s">
+        <v>430</v>
+      </c>
+      <c r="C23" t="s">
+        <v>431</v>
+      </c>
+      <c r="D23" t="s">
+        <v>431</v>
+      </c>
+      <c r="E23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B24" t="s">
+        <v>432</v>
+      </c>
+      <c r="C24" t="s">
+        <v>433</v>
+      </c>
+      <c r="D24" t="s">
+        <v>433</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B25" t="s">
+        <v>434</v>
+      </c>
+      <c r="C25" t="s">
+        <v>435</v>
+      </c>
+      <c r="D25" t="s">
+        <v>435</v>
+      </c>
+      <c r="E25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>436</v>
+      </c>
+      <c r="C26" t="s">
+        <v>437</v>
+      </c>
+      <c r="D26" t="s">
+        <v>437</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
+        <v>438</v>
+      </c>
+      <c r="C27" t="s">
+        <v>439</v>
+      </c>
+      <c r="D27" t="s">
+        <v>439</v>
+      </c>
+      <c r="E27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B28" t="s">
+        <v>440</v>
+      </c>
+      <c r="C28" t="s">
+        <v>441</v>
+      </c>
+      <c r="D28" t="s">
+        <v>441</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B29" t="s">
+        <v>442</v>
+      </c>
+      <c r="C29" t="s">
+        <v>443</v>
+      </c>
+      <c r="D29" t="s">
+        <v>443</v>
+      </c>
+      <c r="E29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B30" t="s">
+        <v>444</v>
+      </c>
+      <c r="C30" t="s">
+        <v>445</v>
+      </c>
+      <c r="D30" t="s">
+        <v>445</v>
+      </c>
+      <c r="E30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B31" t="s">
+        <v>446</v>
+      </c>
+      <c r="C31" t="s">
+        <v>447</v>
+      </c>
+      <c r="D31" t="s">
+        <v>447</v>
+      </c>
+      <c r="E31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B32" t="s">
+        <v>448</v>
+      </c>
+      <c r="C32" t="s">
+        <v>449</v>
+      </c>
+      <c r="D32" t="s">
+        <v>449</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B33" t="s">
+        <v>450</v>
+      </c>
+      <c r="C33" t="s">
+        <v>451</v>
+      </c>
+      <c r="D33" t="s">
+        <v>451</v>
+      </c>
+      <c r="E33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B34" t="s">
+        <v>452</v>
+      </c>
+      <c r="C34" t="s">
+        <v>453</v>
+      </c>
+      <c r="D34" t="s">
+        <v>453</v>
+      </c>
+      <c r="E34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B35" t="s">
+        <v>454</v>
+      </c>
+      <c r="C35" t="s">
+        <v>455</v>
+      </c>
+      <c r="D35" t="s">
+        <v>455</v>
+      </c>
+      <c r="E35" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B36" t="s">
+        <v>456</v>
+      </c>
+      <c r="C36" t="s">
+        <v>457</v>
+      </c>
+      <c r="D36" t="s">
+        <v>457</v>
+      </c>
+      <c r="E36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B37" t="s">
+        <v>458</v>
+      </c>
+      <c r="C37" t="s">
+        <v>459</v>
+      </c>
+      <c r="D37" t="s">
+        <v>459</v>
+      </c>
+      <c r="E37" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B38" t="s">
+        <v>460</v>
+      </c>
+      <c r="C38" t="s">
+        <v>461</v>
+      </c>
+      <c r="D38" t="s">
+        <v>461</v>
+      </c>
+      <c r="E38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B39" t="s">
+        <v>462</v>
+      </c>
+      <c r="C39" t="s">
+        <v>463</v>
+      </c>
+      <c r="D39" t="s">
+        <v>463</v>
+      </c>
+      <c r="E39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B40" t="s">
+        <v>464</v>
+      </c>
+      <c r="C40" t="s">
+        <v>465</v>
+      </c>
+      <c r="D40" t="s">
+        <v>465</v>
+      </c>
+      <c r="E40" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B41" t="s">
+        <v>466</v>
+      </c>
+      <c r="C41" t="s">
+        <v>467</v>
+      </c>
+      <c r="D41" t="s">
+        <v>467</v>
+      </c>
+      <c r="E41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B42" t="s">
+        <v>468</v>
+      </c>
+      <c r="C42" t="s">
+        <v>469</v>
+      </c>
+      <c r="D42" t="s">
+        <v>469</v>
+      </c>
+      <c r="E42" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B43" t="s">
+        <v>470</v>
+      </c>
+      <c r="C43" t="s">
+        <v>471</v>
+      </c>
+      <c r="D43" t="s">
+        <v>471</v>
+      </c>
+      <c r="E43" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B44" t="s">
+        <v>472</v>
+      </c>
+      <c r="C44" t="s">
+        <v>473</v>
+      </c>
+      <c r="D44" t="s">
+        <v>473</v>
+      </c>
+      <c r="E44" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B45" t="s">
+        <v>474</v>
+      </c>
+      <c r="C45" t="s">
+        <v>475</v>
+      </c>
+      <c r="D45" t="s">
+        <v>475</v>
+      </c>
+      <c r="E45" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B46" t="s">
+        <v>476</v>
+      </c>
+      <c r="C46" t="s">
+        <v>477</v>
+      </c>
+      <c r="D46" t="s">
+        <v>477</v>
+      </c>
+      <c r="E46" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B47" t="s">
+        <v>478</v>
+      </c>
+      <c r="C47" t="s">
+        <v>479</v>
+      </c>
+      <c r="D47" t="s">
+        <v>479</v>
+      </c>
+      <c r="E47" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B48" t="s">
+        <v>480</v>
+      </c>
+      <c r="C48" t="s">
+        <v>481</v>
+      </c>
+      <c r="D48" t="s">
+        <v>481</v>
+      </c>
+      <c r="E48" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1263974-0D8C-4D69-9B9F-23A34D418A88}">
   <dimension ref="B9:E41"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7520,13 +8081,13 @@
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>406</v>
+        <v>482</v>
       </c>
       <c r="C11" t="s">
-        <v>407</v>
+        <v>483</v>
       </c>
       <c r="D11" t="s">
-        <v>407</v>
+        <v>483</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -7534,13 +8095,13 @@
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>408</v>
+        <v>484</v>
       </c>
       <c r="C12" t="s">
-        <v>409</v>
+        <v>485</v>
       </c>
       <c r="D12" t="s">
-        <v>409</v>
+        <v>485</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -7548,13 +8109,13 @@
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>410</v>
+        <v>486</v>
       </c>
       <c r="C13" t="s">
-        <v>411</v>
+        <v>487</v>
       </c>
       <c r="D13" t="s">
-        <v>411</v>
+        <v>487</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -7562,13 +8123,13 @@
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>412</v>
+        <v>488</v>
       </c>
       <c r="C14" t="s">
-        <v>413</v>
+        <v>489</v>
       </c>
       <c r="D14" t="s">
-        <v>413</v>
+        <v>489</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -7576,13 +8137,13 @@
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>414</v>
+        <v>490</v>
       </c>
       <c r="C15" t="s">
-        <v>415</v>
+        <v>491</v>
       </c>
       <c r="D15" t="s">
-        <v>415</v>
+        <v>491</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -7590,13 +8151,13 @@
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>416</v>
+        <v>492</v>
       </c>
       <c r="C16" t="s">
-        <v>417</v>
+        <v>493</v>
       </c>
       <c r="D16" t="s">
-        <v>417</v>
+        <v>493</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -7604,13 +8165,13 @@
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>418</v>
+        <v>494</v>
       </c>
       <c r="C17" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="D17" t="s">
-        <v>419</v>
+        <v>495</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -7618,13 +8179,13 @@
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>420</v>
+        <v>496</v>
       </c>
       <c r="C18" t="s">
-        <v>421</v>
+        <v>497</v>
       </c>
       <c r="D18" t="s">
-        <v>421</v>
+        <v>497</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
@@ -7632,13 +8193,13 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>422</v>
+        <v>498</v>
       </c>
       <c r="C19" t="s">
-        <v>423</v>
+        <v>499</v>
       </c>
       <c r="D19" t="s">
-        <v>423</v>
+        <v>499</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -7646,13 +8207,13 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>424</v>
+        <v>500</v>
       </c>
       <c r="C20" t="s">
-        <v>425</v>
+        <v>501</v>
       </c>
       <c r="D20" t="s">
-        <v>425</v>
+        <v>501</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
@@ -7660,13 +8221,13 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>426</v>
+        <v>502</v>
       </c>
       <c r="C21" t="s">
-        <v>427</v>
+        <v>503</v>
       </c>
       <c r="D21" t="s">
-        <v>427</v>
+        <v>503</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
@@ -7674,13 +8235,13 @@
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>428</v>
+        <v>504</v>
       </c>
       <c r="C22" t="s">
-        <v>429</v>
+        <v>505</v>
       </c>
       <c r="D22" t="s">
-        <v>429</v>
+        <v>505</v>
       </c>
       <c r="E22" t="s">
         <v>7</v>
@@ -7688,13 +8249,13 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>430</v>
+        <v>506</v>
       </c>
       <c r="C23" t="s">
-        <v>431</v>
+        <v>507</v>
       </c>
       <c r="D23" t="s">
-        <v>431</v>
+        <v>507</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
@@ -7702,13 +8263,13 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>432</v>
+        <v>508</v>
       </c>
       <c r="C24" t="s">
-        <v>433</v>
+        <v>509</v>
       </c>
       <c r="D24" t="s">
-        <v>433</v>
+        <v>509</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
@@ -7716,13 +8277,13 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>434</v>
+        <v>510</v>
       </c>
       <c r="C25" t="s">
-        <v>435</v>
+        <v>511</v>
       </c>
       <c r="D25" t="s">
-        <v>435</v>
+        <v>511</v>
       </c>
       <c r="E25" t="s">
         <v>7</v>
@@ -7730,13 +8291,13 @@
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>436</v>
+        <v>512</v>
       </c>
       <c r="C26" t="s">
-        <v>437</v>
+        <v>513</v>
       </c>
       <c r="D26" t="s">
-        <v>437</v>
+        <v>513</v>
       </c>
       <c r="E26" t="s">
         <v>7</v>
@@ -7744,13 +8305,13 @@
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>438</v>
+        <v>514</v>
       </c>
       <c r="C27" t="s">
-        <v>439</v>
+        <v>515</v>
       </c>
       <c r="D27" t="s">
-        <v>439</v>
+        <v>515</v>
       </c>
       <c r="E27" t="s">
         <v>7</v>
@@ -7758,13 +8319,13 @@
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>440</v>
+        <v>516</v>
       </c>
       <c r="C28" t="s">
-        <v>441</v>
+        <v>517</v>
       </c>
       <c r="D28" t="s">
-        <v>441</v>
+        <v>517</v>
       </c>
       <c r="E28" t="s">
         <v>7</v>
@@ -7772,13 +8333,13 @@
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>442</v>
+        <v>518</v>
       </c>
       <c r="C29" t="s">
-        <v>443</v>
+        <v>519</v>
       </c>
       <c r="D29" t="s">
-        <v>443</v>
+        <v>519</v>
       </c>
       <c r="E29" t="s">
         <v>7</v>
@@ -7786,13 +8347,13 @@
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>444</v>
+        <v>520</v>
       </c>
       <c r="C30" t="s">
-        <v>445</v>
+        <v>521</v>
       </c>
       <c r="D30" t="s">
-        <v>445</v>
+        <v>521</v>
       </c>
       <c r="E30" t="s">
         <v>7</v>
@@ -7800,13 +8361,13 @@
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>446</v>
+        <v>522</v>
       </c>
       <c r="C31" t="s">
-        <v>447</v>
+        <v>523</v>
       </c>
       <c r="D31" t="s">
-        <v>447</v>
+        <v>523</v>
       </c>
       <c r="E31" t="s">
         <v>7</v>
@@ -7814,13 +8375,13 @@
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>448</v>
+        <v>524</v>
       </c>
       <c r="C32" t="s">
-        <v>449</v>
+        <v>525</v>
       </c>
       <c r="D32" t="s">
-        <v>449</v>
+        <v>525</v>
       </c>
       <c r="E32" t="s">
         <v>7</v>
@@ -7828,13 +8389,13 @@
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>450</v>
+        <v>526</v>
       </c>
       <c r="C33" t="s">
-        <v>451</v>
+        <v>527</v>
       </c>
       <c r="D33" t="s">
-        <v>451</v>
+        <v>527</v>
       </c>
       <c r="E33" t="s">
         <v>7</v>
@@ -7842,13 +8403,13 @@
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>452</v>
+        <v>528</v>
       </c>
       <c r="C34" t="s">
-        <v>453</v>
+        <v>529</v>
       </c>
       <c r="D34" t="s">
-        <v>453</v>
+        <v>529</v>
       </c>
       <c r="E34" t="s">
         <v>7</v>
@@ -7856,13 +8417,13 @@
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>454</v>
+        <v>530</v>
       </c>
       <c r="C35" t="s">
-        <v>455</v>
+        <v>531</v>
       </c>
       <c r="D35" t="s">
-        <v>455</v>
+        <v>531</v>
       </c>
       <c r="E35" t="s">
         <v>7</v>
@@ -7870,13 +8431,13 @@
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>456</v>
+        <v>532</v>
       </c>
       <c r="C36" t="s">
-        <v>457</v>
+        <v>533</v>
       </c>
       <c r="D36" t="s">
-        <v>457</v>
+        <v>533</v>
       </c>
       <c r="E36" t="s">
         <v>7</v>
@@ -7884,13 +8445,13 @@
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>458</v>
+        <v>534</v>
       </c>
       <c r="C37" t="s">
-        <v>459</v>
+        <v>535</v>
       </c>
       <c r="D37" t="s">
-        <v>459</v>
+        <v>535</v>
       </c>
       <c r="E37" t="s">
         <v>7</v>
@@ -7898,13 +8459,13 @@
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>460</v>
+        <v>536</v>
       </c>
       <c r="C38" t="s">
-        <v>461</v>
+        <v>537</v>
       </c>
       <c r="D38" t="s">
-        <v>461</v>
+        <v>537</v>
       </c>
       <c r="E38" t="s">
         <v>7</v>
@@ -7912,13 +8473,13 @@
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>462</v>
+        <v>538</v>
       </c>
       <c r="C39" t="s">
-        <v>463</v>
+        <v>539</v>
       </c>
       <c r="D39" t="s">
-        <v>463</v>
+        <v>539</v>
       </c>
       <c r="E39" t="s">
         <v>7</v>
@@ -7926,13 +8487,13 @@
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>464</v>
+        <v>540</v>
       </c>
       <c r="C40" t="s">
-        <v>465</v>
+        <v>541</v>
       </c>
       <c r="D40" t="s">
-        <v>465</v>
+        <v>541</v>
       </c>
       <c r="E40" t="s">
         <v>7</v>
@@ -7940,13 +8501,13 @@
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
-        <v>466</v>
+        <v>542</v>
       </c>
       <c r="C41" t="s">
-        <v>467</v>
+        <v>543</v>
       </c>
       <c r="D41" t="s">
-        <v>467</v>
+        <v>543</v>
       </c>
       <c r="E41" t="s">
         <v>7</v>
@@ -7957,8 +8518,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{002ECF52-D0F6-4C35-BEC0-E6CFCFE890BF}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C87AB9A-59F1-4AAA-B253-5CC47A998B74}">
   <dimension ref="B9:E102"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7983,13 +8544,13 @@
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>468</v>
+        <v>544</v>
       </c>
       <c r="C11" t="s">
-        <v>469</v>
+        <v>545</v>
       </c>
       <c r="D11" t="s">
-        <v>469</v>
+        <v>545</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -7997,13 +8558,13 @@
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>470</v>
+        <v>546</v>
       </c>
       <c r="C12" t="s">
-        <v>471</v>
+        <v>547</v>
       </c>
       <c r="D12" t="s">
-        <v>471</v>
+        <v>547</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -8011,13 +8572,13 @@
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>472</v>
+        <v>548</v>
       </c>
       <c r="C13" t="s">
-        <v>473</v>
+        <v>549</v>
       </c>
       <c r="D13" t="s">
-        <v>473</v>
+        <v>549</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -8025,13 +8586,13 @@
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>474</v>
+        <v>550</v>
       </c>
       <c r="C14" t="s">
-        <v>475</v>
+        <v>551</v>
       </c>
       <c r="D14" t="s">
-        <v>475</v>
+        <v>551</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -8039,13 +8600,13 @@
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>476</v>
+        <v>552</v>
       </c>
       <c r="C15" t="s">
-        <v>477</v>
+        <v>553</v>
       </c>
       <c r="D15" t="s">
-        <v>477</v>
+        <v>553</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -8053,13 +8614,13 @@
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>478</v>
+        <v>554</v>
       </c>
       <c r="C16" t="s">
-        <v>479</v>
+        <v>555</v>
       </c>
       <c r="D16" t="s">
-        <v>479</v>
+        <v>555</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -8067,13 +8628,13 @@
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>480</v>
+        <v>556</v>
       </c>
       <c r="C17" t="s">
-        <v>481</v>
+        <v>557</v>
       </c>
       <c r="D17" t="s">
-        <v>481</v>
+        <v>557</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -8081,13 +8642,13 @@
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>482</v>
+        <v>558</v>
       </c>
       <c r="C18" t="s">
-        <v>483</v>
+        <v>559</v>
       </c>
       <c r="D18" t="s">
-        <v>483</v>
+        <v>559</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
@@ -8095,13 +8656,13 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>484</v>
+        <v>560</v>
       </c>
       <c r="C19" t="s">
-        <v>485</v>
+        <v>561</v>
       </c>
       <c r="D19" t="s">
-        <v>485</v>
+        <v>561</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -8109,13 +8670,13 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>486</v>
+        <v>562</v>
       </c>
       <c r="C20" t="s">
-        <v>487</v>
+        <v>563</v>
       </c>
       <c r="D20" t="s">
-        <v>487</v>
+        <v>563</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
@@ -8123,13 +8684,13 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>488</v>
+        <v>564</v>
       </c>
       <c r="C21" t="s">
-        <v>489</v>
+        <v>565</v>
       </c>
       <c r="D21" t="s">
-        <v>489</v>
+        <v>565</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
@@ -8137,13 +8698,13 @@
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>490</v>
+        <v>566</v>
       </c>
       <c r="C22" t="s">
-        <v>491</v>
+        <v>567</v>
       </c>
       <c r="D22" t="s">
-        <v>491</v>
+        <v>567</v>
       </c>
       <c r="E22" t="s">
         <v>7</v>
@@ -8151,13 +8712,13 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>492</v>
+        <v>568</v>
       </c>
       <c r="C23" t="s">
-        <v>493</v>
+        <v>569</v>
       </c>
       <c r="D23" t="s">
-        <v>493</v>
+        <v>569</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
@@ -8165,13 +8726,13 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>494</v>
+        <v>570</v>
       </c>
       <c r="C24" t="s">
-        <v>495</v>
+        <v>571</v>
       </c>
       <c r="D24" t="s">
-        <v>495</v>
+        <v>571</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
@@ -8179,13 +8740,13 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>496</v>
+        <v>572</v>
       </c>
       <c r="C25" t="s">
-        <v>497</v>
+        <v>573</v>
       </c>
       <c r="D25" t="s">
-        <v>497</v>
+        <v>573</v>
       </c>
       <c r="E25" t="s">
         <v>7</v>
@@ -8193,13 +8754,13 @@
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>498</v>
+        <v>574</v>
       </c>
       <c r="C26" t="s">
-        <v>499</v>
+        <v>575</v>
       </c>
       <c r="D26" t="s">
-        <v>499</v>
+        <v>575</v>
       </c>
       <c r="E26" t="s">
         <v>7</v>
@@ -8207,13 +8768,13 @@
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>500</v>
+        <v>576</v>
       </c>
       <c r="C27" t="s">
-        <v>501</v>
+        <v>577</v>
       </c>
       <c r="D27" t="s">
-        <v>501</v>
+        <v>577</v>
       </c>
       <c r="E27" t="s">
         <v>7</v>
@@ -8221,13 +8782,13 @@
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>502</v>
+        <v>578</v>
       </c>
       <c r="C28" t="s">
-        <v>503</v>
+        <v>579</v>
       </c>
       <c r="D28" t="s">
-        <v>503</v>
+        <v>579</v>
       </c>
       <c r="E28" t="s">
         <v>7</v>
@@ -8235,13 +8796,13 @@
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>504</v>
+        <v>580</v>
       </c>
       <c r="C29" t="s">
-        <v>505</v>
+        <v>581</v>
       </c>
       <c r="D29" t="s">
-        <v>505</v>
+        <v>581</v>
       </c>
       <c r="E29" t="s">
         <v>7</v>
@@ -8249,13 +8810,13 @@
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>506</v>
+        <v>582</v>
       </c>
       <c r="C30" t="s">
-        <v>507</v>
+        <v>583</v>
       </c>
       <c r="D30" t="s">
-        <v>507</v>
+        <v>583</v>
       </c>
       <c r="E30" t="s">
         <v>7</v>
@@ -8263,13 +8824,13 @@
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>508</v>
+        <v>584</v>
       </c>
       <c r="C31" t="s">
-        <v>509</v>
+        <v>585</v>
       </c>
       <c r="D31" t="s">
-        <v>509</v>
+        <v>585</v>
       </c>
       <c r="E31" t="s">
         <v>7</v>
@@ -8277,13 +8838,13 @@
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>510</v>
+        <v>586</v>
       </c>
       <c r="C32" t="s">
-        <v>511</v>
+        <v>587</v>
       </c>
       <c r="D32" t="s">
-        <v>511</v>
+        <v>587</v>
       </c>
       <c r="E32" t="s">
         <v>7</v>
@@ -8291,13 +8852,13 @@
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>512</v>
+        <v>588</v>
       </c>
       <c r="C33" t="s">
-        <v>513</v>
+        <v>589</v>
       </c>
       <c r="D33" t="s">
-        <v>513</v>
+        <v>589</v>
       </c>
       <c r="E33" t="s">
         <v>7</v>
@@ -8305,13 +8866,13 @@
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>514</v>
+        <v>590</v>
       </c>
       <c r="C34" t="s">
-        <v>515</v>
+        <v>591</v>
       </c>
       <c r="D34" t="s">
-        <v>515</v>
+        <v>591</v>
       </c>
       <c r="E34" t="s">
         <v>7</v>
@@ -8319,13 +8880,13 @@
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>516</v>
+        <v>592</v>
       </c>
       <c r="C35" t="s">
-        <v>517</v>
+        <v>593</v>
       </c>
       <c r="D35" t="s">
-        <v>517</v>
+        <v>593</v>
       </c>
       <c r="E35" t="s">
         <v>7</v>
@@ -8333,13 +8894,13 @@
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>518</v>
+        <v>594</v>
       </c>
       <c r="C36" t="s">
-        <v>519</v>
+        <v>595</v>
       </c>
       <c r="D36" t="s">
-        <v>519</v>
+        <v>595</v>
       </c>
       <c r="E36" t="s">
         <v>7</v>
@@ -8347,13 +8908,13 @@
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>520</v>
+        <v>596</v>
       </c>
       <c r="C37" t="s">
-        <v>521</v>
+        <v>597</v>
       </c>
       <c r="D37" t="s">
-        <v>521</v>
+        <v>597</v>
       </c>
       <c r="E37" t="s">
         <v>7</v>
@@ -8361,13 +8922,13 @@
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>522</v>
+        <v>598</v>
       </c>
       <c r="C38" t="s">
-        <v>523</v>
+        <v>599</v>
       </c>
       <c r="D38" t="s">
-        <v>523</v>
+        <v>599</v>
       </c>
       <c r="E38" t="s">
         <v>7</v>
@@ -8375,13 +8936,13 @@
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>524</v>
+        <v>600</v>
       </c>
       <c r="C39" t="s">
-        <v>525</v>
+        <v>601</v>
       </c>
       <c r="D39" t="s">
-        <v>525</v>
+        <v>601</v>
       </c>
       <c r="E39" t="s">
         <v>7</v>
@@ -8389,13 +8950,13 @@
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>526</v>
+        <v>602</v>
       </c>
       <c r="C40" t="s">
-        <v>527</v>
+        <v>603</v>
       </c>
       <c r="D40" t="s">
-        <v>527</v>
+        <v>603</v>
       </c>
       <c r="E40" t="s">
         <v>7</v>
@@ -8403,13 +8964,13 @@
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
-        <v>528</v>
+        <v>604</v>
       </c>
       <c r="C41" t="s">
-        <v>529</v>
+        <v>605</v>
       </c>
       <c r="D41" t="s">
-        <v>529</v>
+        <v>605</v>
       </c>
       <c r="E41" t="s">
         <v>7</v>
@@ -8417,13 +8978,13 @@
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>530</v>
+        <v>606</v>
       </c>
       <c r="C42" t="s">
-        <v>531</v>
+        <v>607</v>
       </c>
       <c r="D42" t="s">
-        <v>531</v>
+        <v>607</v>
       </c>
       <c r="E42" t="s">
         <v>7</v>
@@ -8431,13 +8992,13 @@
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>532</v>
+        <v>608</v>
       </c>
       <c r="C43" t="s">
-        <v>533</v>
+        <v>609</v>
       </c>
       <c r="D43" t="s">
-        <v>533</v>
+        <v>609</v>
       </c>
       <c r="E43" t="s">
         <v>7</v>
@@ -8445,13 +9006,13 @@
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
-        <v>534</v>
+        <v>610</v>
       </c>
       <c r="C44" t="s">
-        <v>535</v>
+        <v>611</v>
       </c>
       <c r="D44" t="s">
-        <v>535</v>
+        <v>611</v>
       </c>
       <c r="E44" t="s">
         <v>7</v>
@@ -8459,13 +9020,13 @@
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
-        <v>536</v>
+        <v>612</v>
       </c>
       <c r="C45" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
       <c r="D45" t="s">
-        <v>537</v>
+        <v>613</v>
       </c>
       <c r="E45" t="s">
         <v>7</v>
@@ -8473,13 +9034,13 @@
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
-        <v>538</v>
+        <v>614</v>
       </c>
       <c r="C46" t="s">
-        <v>539</v>
+        <v>615</v>
       </c>
       <c r="D46" t="s">
-        <v>539</v>
+        <v>615</v>
       </c>
       <c r="E46" t="s">
         <v>7</v>
@@ -8487,13 +9048,13 @@
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>540</v>
+        <v>616</v>
       </c>
       <c r="C47" t="s">
-        <v>541</v>
+        <v>617</v>
       </c>
       <c r="D47" t="s">
-        <v>541</v>
+        <v>617</v>
       </c>
       <c r="E47" t="s">
         <v>7</v>
@@ -8501,13 +9062,13 @@
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>542</v>
+        <v>618</v>
       </c>
       <c r="C48" t="s">
-        <v>543</v>
+        <v>619</v>
       </c>
       <c r="D48" t="s">
-        <v>543</v>
+        <v>619</v>
       </c>
       <c r="E48" t="s">
         <v>7</v>
@@ -8515,13 +9076,13 @@
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
-        <v>544</v>
+        <v>620</v>
       </c>
       <c r="C49" t="s">
-        <v>545</v>
+        <v>621</v>
       </c>
       <c r="D49" t="s">
-        <v>545</v>
+        <v>621</v>
       </c>
       <c r="E49" t="s">
         <v>7</v>
@@ -8529,13 +9090,13 @@
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
-        <v>546</v>
+        <v>622</v>
       </c>
       <c r="C50" t="s">
-        <v>547</v>
+        <v>623</v>
       </c>
       <c r="D50" t="s">
-        <v>547</v>
+        <v>623</v>
       </c>
       <c r="E50" t="s">
         <v>7</v>
@@ -8543,13 +9104,13 @@
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
-        <v>548</v>
+        <v>624</v>
       </c>
       <c r="C51" t="s">
-        <v>549</v>
+        <v>625</v>
       </c>
       <c r="D51" t="s">
-        <v>549</v>
+        <v>625</v>
       </c>
       <c r="E51" t="s">
         <v>7</v>
@@ -8557,13 +9118,13 @@
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
-        <v>550</v>
+        <v>626</v>
       </c>
       <c r="C52" t="s">
-        <v>551</v>
+        <v>627</v>
       </c>
       <c r="D52" t="s">
-        <v>551</v>
+        <v>627</v>
       </c>
       <c r="E52" t="s">
         <v>7</v>
@@ -8571,13 +9132,13 @@
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
-        <v>552</v>
+        <v>628</v>
       </c>
       <c r="C53" t="s">
-        <v>553</v>
+        <v>629</v>
       </c>
       <c r="D53" t="s">
-        <v>553</v>
+        <v>629</v>
       </c>
       <c r="E53" t="s">
         <v>7</v>
@@ -8585,13 +9146,13 @@
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
-        <v>554</v>
+        <v>630</v>
       </c>
       <c r="C54" t="s">
-        <v>555</v>
+        <v>631</v>
       </c>
       <c r="D54" t="s">
-        <v>555</v>
+        <v>631</v>
       </c>
       <c r="E54" t="s">
         <v>7</v>
@@ -8599,13 +9160,13 @@
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
-        <v>556</v>
+        <v>632</v>
       </c>
       <c r="C55" t="s">
-        <v>557</v>
+        <v>633</v>
       </c>
       <c r="D55" t="s">
-        <v>557</v>
+        <v>633</v>
       </c>
       <c r="E55" t="s">
         <v>7</v>
@@ -8613,13 +9174,13 @@
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
-        <v>558</v>
+        <v>634</v>
       </c>
       <c r="C56" t="s">
-        <v>559</v>
+        <v>635</v>
       </c>
       <c r="D56" t="s">
-        <v>559</v>
+        <v>635</v>
       </c>
       <c r="E56" t="s">
         <v>7</v>
@@ -8627,13 +9188,13 @@
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>560</v>
+        <v>636</v>
       </c>
       <c r="C57" t="s">
-        <v>561</v>
+        <v>637</v>
       </c>
       <c r="D57" t="s">
-        <v>561</v>
+        <v>637</v>
       </c>
       <c r="E57" t="s">
         <v>7</v>
@@ -8641,13 +9202,13 @@
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>562</v>
+        <v>638</v>
       </c>
       <c r="C58" t="s">
-        <v>563</v>
+        <v>639</v>
       </c>
       <c r="D58" t="s">
-        <v>563</v>
+        <v>639</v>
       </c>
       <c r="E58" t="s">
         <v>7</v>
@@ -8655,13 +9216,13 @@
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
-        <v>564</v>
+        <v>640</v>
       </c>
       <c r="C59" t="s">
-        <v>565</v>
+        <v>641</v>
       </c>
       <c r="D59" t="s">
-        <v>565</v>
+        <v>641</v>
       </c>
       <c r="E59" t="s">
         <v>7</v>
@@ -8669,13 +9230,13 @@
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
-        <v>566</v>
+        <v>642</v>
       </c>
       <c r="C60" t="s">
-        <v>567</v>
+        <v>643</v>
       </c>
       <c r="D60" t="s">
-        <v>567</v>
+        <v>643</v>
       </c>
       <c r="E60" t="s">
         <v>7</v>
@@ -8683,13 +9244,13 @@
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
-        <v>568</v>
+        <v>644</v>
       </c>
       <c r="C61" t="s">
-        <v>569</v>
+        <v>645</v>
       </c>
       <c r="D61" t="s">
-        <v>569</v>
+        <v>645</v>
       </c>
       <c r="E61" t="s">
         <v>7</v>
@@ -8697,13 +9258,13 @@
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
-        <v>570</v>
+        <v>646</v>
       </c>
       <c r="C62" t="s">
-        <v>571</v>
+        <v>647</v>
       </c>
       <c r="D62" t="s">
-        <v>571</v>
+        <v>647</v>
       </c>
       <c r="E62" t="s">
         <v>7</v>
@@ -8711,13 +9272,13 @@
     </row>
     <row r="63" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
-        <v>572</v>
+        <v>648</v>
       </c>
       <c r="C63" t="s">
-        <v>573</v>
+        <v>649</v>
       </c>
       <c r="D63" t="s">
-        <v>573</v>
+        <v>649</v>
       </c>
       <c r="E63" t="s">
         <v>7</v>
@@ -8725,13 +9286,13 @@
     </row>
     <row r="64" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
-        <v>574</v>
+        <v>650</v>
       </c>
       <c r="C64" t="s">
-        <v>575</v>
+        <v>651</v>
       </c>
       <c r="D64" t="s">
-        <v>575</v>
+        <v>651</v>
       </c>
       <c r="E64" t="s">
         <v>7</v>
@@ -8739,13 +9300,13 @@
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
-        <v>576</v>
+        <v>652</v>
       </c>
       <c r="C65" t="s">
-        <v>577</v>
+        <v>653</v>
       </c>
       <c r="D65" t="s">
-        <v>577</v>
+        <v>653</v>
       </c>
       <c r="E65" t="s">
         <v>7</v>
@@ -8753,13 +9314,13 @@
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
-        <v>578</v>
+        <v>654</v>
       </c>
       <c r="C66" t="s">
-        <v>579</v>
+        <v>655</v>
       </c>
       <c r="D66" t="s">
-        <v>579</v>
+        <v>655</v>
       </c>
       <c r="E66" t="s">
         <v>7</v>
@@ -8767,13 +9328,13 @@
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
-        <v>580</v>
+        <v>656</v>
       </c>
       <c r="C67" t="s">
-        <v>581</v>
+        <v>657</v>
       </c>
       <c r="D67" t="s">
-        <v>581</v>
+        <v>657</v>
       </c>
       <c r="E67" t="s">
         <v>7</v>
@@ -8781,13 +9342,13 @@
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
-        <v>582</v>
+        <v>658</v>
       </c>
       <c r="C68" t="s">
-        <v>583</v>
+        <v>659</v>
       </c>
       <c r="D68" t="s">
-        <v>583</v>
+        <v>659</v>
       </c>
       <c r="E68" t="s">
         <v>7</v>
@@ -8795,13 +9356,13 @@
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
-        <v>584</v>
+        <v>660</v>
       </c>
       <c r="C69" t="s">
-        <v>585</v>
+        <v>661</v>
       </c>
       <c r="D69" t="s">
-        <v>585</v>
+        <v>661</v>
       </c>
       <c r="E69" t="s">
         <v>7</v>
@@ -8809,13 +9370,13 @@
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
-        <v>586</v>
+        <v>662</v>
       </c>
       <c r="C70" t="s">
-        <v>587</v>
+        <v>663</v>
       </c>
       <c r="D70" t="s">
-        <v>587</v>
+        <v>663</v>
       </c>
       <c r="E70" t="s">
         <v>7</v>
@@ -8823,13 +9384,13 @@
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
-        <v>588</v>
+        <v>664</v>
       </c>
       <c r="C71" t="s">
-        <v>589</v>
+        <v>665</v>
       </c>
       <c r="D71" t="s">
-        <v>589</v>
+        <v>665</v>
       </c>
       <c r="E71" t="s">
         <v>7</v>
@@ -8837,13 +9398,13 @@
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
-        <v>590</v>
+        <v>666</v>
       </c>
       <c r="C72" t="s">
-        <v>591</v>
+        <v>667</v>
       </c>
       <c r="D72" t="s">
-        <v>591</v>
+        <v>667</v>
       </c>
       <c r="E72" t="s">
         <v>7</v>
@@ -8851,13 +9412,13 @@
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
-        <v>592</v>
+        <v>668</v>
       </c>
       <c r="C73" t="s">
-        <v>593</v>
+        <v>669</v>
       </c>
       <c r="D73" t="s">
-        <v>593</v>
+        <v>669</v>
       </c>
       <c r="E73" t="s">
         <v>7</v>
@@ -8865,13 +9426,13 @@
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
-        <v>594</v>
+        <v>670</v>
       </c>
       <c r="C74" t="s">
-        <v>595</v>
+        <v>671</v>
       </c>
       <c r="D74" t="s">
-        <v>595</v>
+        <v>671</v>
       </c>
       <c r="E74" t="s">
         <v>7</v>
@@ -8879,13 +9440,13 @@
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B75" t="s">
-        <v>596</v>
+        <v>672</v>
       </c>
       <c r="C75" t="s">
-        <v>597</v>
+        <v>673</v>
       </c>
       <c r="D75" t="s">
-        <v>597</v>
+        <v>673</v>
       </c>
       <c r="E75" t="s">
         <v>7</v>
@@ -8893,13 +9454,13 @@
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B76" t="s">
-        <v>598</v>
+        <v>674</v>
       </c>
       <c r="C76" t="s">
-        <v>599</v>
+        <v>675</v>
       </c>
       <c r="D76" t="s">
-        <v>599</v>
+        <v>675</v>
       </c>
       <c r="E76" t="s">
         <v>7</v>
@@ -8907,13 +9468,13 @@
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
-        <v>600</v>
+        <v>676</v>
       </c>
       <c r="C77" t="s">
-        <v>601</v>
+        <v>677</v>
       </c>
       <c r="D77" t="s">
-        <v>601</v>
+        <v>677</v>
       </c>
       <c r="E77" t="s">
         <v>7</v>
@@ -8921,13 +9482,13 @@
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B78" t="s">
-        <v>602</v>
+        <v>678</v>
       </c>
       <c r="C78" t="s">
-        <v>603</v>
+        <v>679</v>
       </c>
       <c r="D78" t="s">
-        <v>603</v>
+        <v>679</v>
       </c>
       <c r="E78" t="s">
         <v>7</v>
@@ -8935,13 +9496,13 @@
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B79" t="s">
-        <v>604</v>
+        <v>680</v>
       </c>
       <c r="C79" t="s">
-        <v>605</v>
+        <v>681</v>
       </c>
       <c r="D79" t="s">
-        <v>605</v>
+        <v>681</v>
       </c>
       <c r="E79" t="s">
         <v>7</v>
@@ -8949,13 +9510,13 @@
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B80" t="s">
-        <v>606</v>
+        <v>682</v>
       </c>
       <c r="C80" t="s">
-        <v>607</v>
+        <v>683</v>
       </c>
       <c r="D80" t="s">
-        <v>607</v>
+        <v>683</v>
       </c>
       <c r="E80" t="s">
         <v>7</v>
@@ -8963,13 +9524,13 @@
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B81" t="s">
-        <v>608</v>
+        <v>684</v>
       </c>
       <c r="C81" t="s">
-        <v>609</v>
+        <v>685</v>
       </c>
       <c r="D81" t="s">
-        <v>609</v>
+        <v>685</v>
       </c>
       <c r="E81" t="s">
         <v>7</v>
@@ -8977,13 +9538,13 @@
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B82" t="s">
-        <v>610</v>
+        <v>686</v>
       </c>
       <c r="C82" t="s">
-        <v>611</v>
+        <v>687</v>
       </c>
       <c r="D82" t="s">
-        <v>611</v>
+        <v>687</v>
       </c>
       <c r="E82" t="s">
         <v>7</v>
@@ -8991,13 +9552,13 @@
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B83" t="s">
-        <v>612</v>
+        <v>688</v>
       </c>
       <c r="C83" t="s">
-        <v>613</v>
+        <v>689</v>
       </c>
       <c r="D83" t="s">
-        <v>613</v>
+        <v>689</v>
       </c>
       <c r="E83" t="s">
         <v>7</v>
@@ -9005,13 +9566,13 @@
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B84" t="s">
-        <v>614</v>
+        <v>690</v>
       </c>
       <c r="C84" t="s">
-        <v>615</v>
+        <v>691</v>
       </c>
       <c r="D84" t="s">
-        <v>615</v>
+        <v>691</v>
       </c>
       <c r="E84" t="s">
         <v>7</v>
@@ -9019,13 +9580,13 @@
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B85" t="s">
-        <v>616</v>
+        <v>692</v>
       </c>
       <c r="C85" t="s">
-        <v>617</v>
+        <v>693</v>
       </c>
       <c r="D85" t="s">
-        <v>617</v>
+        <v>693</v>
       </c>
       <c r="E85" t="s">
         <v>7</v>
@@ -9033,13 +9594,13 @@
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B86" t="s">
-        <v>618</v>
+        <v>694</v>
       </c>
       <c r="C86" t="s">
-        <v>619</v>
+        <v>695</v>
       </c>
       <c r="D86" t="s">
-        <v>619</v>
+        <v>695</v>
       </c>
       <c r="E86" t="s">
         <v>7</v>
@@ -9047,13 +9608,13 @@
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B87" t="s">
-        <v>620</v>
+        <v>696</v>
       </c>
       <c r="C87" t="s">
-        <v>621</v>
+        <v>697</v>
       </c>
       <c r="D87" t="s">
-        <v>621</v>
+        <v>697</v>
       </c>
       <c r="E87" t="s">
         <v>7</v>
@@ -9061,13 +9622,13 @@
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B88" t="s">
-        <v>622</v>
+        <v>698</v>
       </c>
       <c r="C88" t="s">
-        <v>623</v>
+        <v>699</v>
       </c>
       <c r="D88" t="s">
-        <v>623</v>
+        <v>699</v>
       </c>
       <c r="E88" t="s">
         <v>7</v>
@@ -9075,13 +9636,13 @@
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B89" t="s">
-        <v>624</v>
+        <v>700</v>
       </c>
       <c r="C89" t="s">
-        <v>625</v>
+        <v>701</v>
       </c>
       <c r="D89" t="s">
-        <v>625</v>
+        <v>701</v>
       </c>
       <c r="E89" t="s">
         <v>7</v>
@@ -9089,13 +9650,13 @@
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B90" t="s">
-        <v>626</v>
+        <v>702</v>
       </c>
       <c r="C90" t="s">
-        <v>627</v>
+        <v>703</v>
       </c>
       <c r="D90" t="s">
-        <v>627</v>
+        <v>703</v>
       </c>
       <c r="E90" t="s">
         <v>7</v>
@@ -9103,13 +9664,13 @@
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B91" t="s">
-        <v>628</v>
+        <v>704</v>
       </c>
       <c r="C91" t="s">
-        <v>629</v>
+        <v>705</v>
       </c>
       <c r="D91" t="s">
-        <v>629</v>
+        <v>705</v>
       </c>
       <c r="E91" t="s">
         <v>7</v>
@@ -9117,13 +9678,13 @@
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B92" t="s">
-        <v>630</v>
+        <v>706</v>
       </c>
       <c r="C92" t="s">
-        <v>631</v>
+        <v>707</v>
       </c>
       <c r="D92" t="s">
-        <v>631</v>
+        <v>707</v>
       </c>
       <c r="E92" t="s">
         <v>7</v>
@@ -9131,13 +9692,13 @@
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B93" t="s">
-        <v>632</v>
+        <v>708</v>
       </c>
       <c r="C93" t="s">
-        <v>633</v>
+        <v>709</v>
       </c>
       <c r="D93" t="s">
-        <v>633</v>
+        <v>709</v>
       </c>
       <c r="E93" t="s">
         <v>7</v>
@@ -9145,13 +9706,13 @@
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B94" t="s">
-        <v>634</v>
+        <v>710</v>
       </c>
       <c r="C94" t="s">
-        <v>635</v>
+        <v>711</v>
       </c>
       <c r="D94" t="s">
-        <v>635</v>
+        <v>711</v>
       </c>
       <c r="E94" t="s">
         <v>7</v>
@@ -9159,13 +9720,13 @@
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B95" t="s">
-        <v>636</v>
+        <v>712</v>
       </c>
       <c r="C95" t="s">
-        <v>637</v>
+        <v>713</v>
       </c>
       <c r="D95" t="s">
-        <v>637</v>
+        <v>713</v>
       </c>
       <c r="E95" t="s">
         <v>7</v>
@@ -9173,13 +9734,13 @@
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B96" t="s">
-        <v>638</v>
+        <v>714</v>
       </c>
       <c r="C96" t="s">
-        <v>639</v>
+        <v>715</v>
       </c>
       <c r="D96" t="s">
-        <v>639</v>
+        <v>715</v>
       </c>
       <c r="E96" t="s">
         <v>7</v>
@@ -9187,13 +9748,13 @@
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B97" t="s">
-        <v>640</v>
+        <v>716</v>
       </c>
       <c r="C97" t="s">
-        <v>641</v>
+        <v>717</v>
       </c>
       <c r="D97" t="s">
-        <v>641</v>
+        <v>717</v>
       </c>
       <c r="E97" t="s">
         <v>7</v>
@@ -9201,13 +9762,13 @@
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B98" t="s">
-        <v>642</v>
+        <v>718</v>
       </c>
       <c r="C98" t="s">
-        <v>643</v>
+        <v>719</v>
       </c>
       <c r="D98" t="s">
-        <v>643</v>
+        <v>719</v>
       </c>
       <c r="E98" t="s">
         <v>7</v>
@@ -9215,13 +9776,13 @@
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B99" t="s">
-        <v>644</v>
+        <v>720</v>
       </c>
       <c r="C99" t="s">
-        <v>645</v>
+        <v>721</v>
       </c>
       <c r="D99" t="s">
-        <v>645</v>
+        <v>721</v>
       </c>
       <c r="E99" t="s">
         <v>7</v>
@@ -9229,13 +9790,13 @@
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B100" t="s">
-        <v>646</v>
+        <v>722</v>
       </c>
       <c r="C100" t="s">
-        <v>647</v>
+        <v>723</v>
       </c>
       <c r="D100" t="s">
-        <v>647</v>
+        <v>723</v>
       </c>
       <c r="E100" t="s">
         <v>7</v>
@@ -9243,13 +9804,13 @@
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B101" t="s">
-        <v>648</v>
+        <v>724</v>
       </c>
       <c r="C101" t="s">
-        <v>649</v>
+        <v>725</v>
       </c>
       <c r="D101" t="s">
-        <v>649</v>
+        <v>725</v>
       </c>
       <c r="E101" t="s">
         <v>7</v>
@@ -9257,13 +9818,13 @@
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B102" t="s">
-        <v>650</v>
+        <v>726</v>
       </c>
       <c r="C102" t="s">
-        <v>651</v>
+        <v>727</v>
       </c>
       <c r="D102" t="s">
-        <v>651</v>
+        <v>727</v>
       </c>
       <c r="E102" t="s">
         <v>7</v>
@@ -9274,8 +9835,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6B24935-0419-4114-8AA6-5A7F5DD2B3B1}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{437BCD7D-0512-4953-BD62-0585EE34F001}">
   <dimension ref="B9:E49"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9300,13 +9861,13 @@
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>652</v>
+        <v>728</v>
       </c>
       <c r="C11" t="s">
-        <v>653</v>
+        <v>729</v>
       </c>
       <c r="D11" t="s">
-        <v>653</v>
+        <v>729</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -9314,13 +9875,13 @@
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>654</v>
+        <v>730</v>
       </c>
       <c r="C12" t="s">
-        <v>655</v>
+        <v>731</v>
       </c>
       <c r="D12" t="s">
-        <v>655</v>
+        <v>731</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -9328,13 +9889,13 @@
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>656</v>
+        <v>732</v>
       </c>
       <c r="C13" t="s">
-        <v>657</v>
+        <v>733</v>
       </c>
       <c r="D13" t="s">
-        <v>657</v>
+        <v>733</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -9342,13 +9903,13 @@
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>658</v>
+        <v>734</v>
       </c>
       <c r="C14" t="s">
-        <v>659</v>
+        <v>735</v>
       </c>
       <c r="D14" t="s">
-        <v>659</v>
+        <v>735</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -9356,13 +9917,13 @@
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>660</v>
+        <v>736</v>
       </c>
       <c r="C15" t="s">
-        <v>661</v>
+        <v>737</v>
       </c>
       <c r="D15" t="s">
-        <v>661</v>
+        <v>737</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -9370,13 +9931,13 @@
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>662</v>
+        <v>738</v>
       </c>
       <c r="C16" t="s">
-        <v>663</v>
+        <v>739</v>
       </c>
       <c r="D16" t="s">
-        <v>663</v>
+        <v>739</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -9384,13 +9945,13 @@
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>664</v>
+        <v>740</v>
       </c>
       <c r="C17" t="s">
-        <v>665</v>
+        <v>741</v>
       </c>
       <c r="D17" t="s">
-        <v>665</v>
+        <v>741</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -9398,13 +9959,13 @@
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>666</v>
+        <v>742</v>
       </c>
       <c r="C18" t="s">
-        <v>667</v>
+        <v>743</v>
       </c>
       <c r="D18" t="s">
-        <v>667</v>
+        <v>743</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
@@ -9412,13 +9973,13 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>668</v>
+        <v>744</v>
       </c>
       <c r="C19" t="s">
-        <v>669</v>
+        <v>745</v>
       </c>
       <c r="D19" t="s">
-        <v>669</v>
+        <v>745</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -9426,13 +9987,13 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>670</v>
+        <v>746</v>
       </c>
       <c r="C20" t="s">
-        <v>671</v>
+        <v>747</v>
       </c>
       <c r="D20" t="s">
-        <v>671</v>
+        <v>747</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
@@ -9440,13 +10001,13 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>672</v>
+        <v>748</v>
       </c>
       <c r="C21" t="s">
-        <v>673</v>
+        <v>749</v>
       </c>
       <c r="D21" t="s">
-        <v>673</v>
+        <v>749</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
@@ -9454,13 +10015,13 @@
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>674</v>
+        <v>750</v>
       </c>
       <c r="C22" t="s">
-        <v>675</v>
+        <v>751</v>
       </c>
       <c r="D22" t="s">
-        <v>675</v>
+        <v>751</v>
       </c>
       <c r="E22" t="s">
         <v>7</v>
@@ -9468,13 +10029,13 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>676</v>
+        <v>752</v>
       </c>
       <c r="C23" t="s">
-        <v>677</v>
+        <v>753</v>
       </c>
       <c r="D23" t="s">
-        <v>677</v>
+        <v>753</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
@@ -9482,13 +10043,13 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>678</v>
+        <v>754</v>
       </c>
       <c r="C24" t="s">
-        <v>679</v>
+        <v>755</v>
       </c>
       <c r="D24" t="s">
-        <v>679</v>
+        <v>755</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
@@ -9496,13 +10057,13 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>680</v>
+        <v>756</v>
       </c>
       <c r="C25" t="s">
-        <v>681</v>
+        <v>757</v>
       </c>
       <c r="D25" t="s">
-        <v>681</v>
+        <v>757</v>
       </c>
       <c r="E25" t="s">
         <v>7</v>
@@ -9510,13 +10071,13 @@
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>682</v>
+        <v>758</v>
       </c>
       <c r="C26" t="s">
-        <v>683</v>
+        <v>759</v>
       </c>
       <c r="D26" t="s">
-        <v>683</v>
+        <v>759</v>
       </c>
       <c r="E26" t="s">
         <v>7</v>
@@ -9524,13 +10085,13 @@
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>684</v>
+        <v>760</v>
       </c>
       <c r="C27" t="s">
-        <v>685</v>
+        <v>761</v>
       </c>
       <c r="D27" t="s">
-        <v>685</v>
+        <v>761</v>
       </c>
       <c r="E27" t="s">
         <v>7</v>
@@ -9538,13 +10099,13 @@
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>686</v>
+        <v>762</v>
       </c>
       <c r="C28" t="s">
-        <v>687</v>
+        <v>763</v>
       </c>
       <c r="D28" t="s">
-        <v>687</v>
+        <v>763</v>
       </c>
       <c r="E28" t="s">
         <v>7</v>
@@ -9552,13 +10113,13 @@
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>688</v>
+        <v>764</v>
       </c>
       <c r="C29" t="s">
-        <v>689</v>
+        <v>765</v>
       </c>
       <c r="D29" t="s">
-        <v>689</v>
+        <v>765</v>
       </c>
       <c r="E29" t="s">
         <v>7</v>
@@ -9566,13 +10127,13 @@
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>690</v>
+        <v>766</v>
       </c>
       <c r="C30" t="s">
-        <v>691</v>
+        <v>767</v>
       </c>
       <c r="D30" t="s">
-        <v>691</v>
+        <v>767</v>
       </c>
       <c r="E30" t="s">
         <v>7</v>
@@ -9580,13 +10141,13 @@
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>692</v>
+        <v>768</v>
       </c>
       <c r="C31" t="s">
-        <v>693</v>
+        <v>769</v>
       </c>
       <c r="D31" t="s">
-        <v>693</v>
+        <v>769</v>
       </c>
       <c r="E31" t="s">
         <v>7</v>
@@ -9594,13 +10155,13 @@
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>694</v>
+        <v>770</v>
       </c>
       <c r="C32" t="s">
-        <v>695</v>
+        <v>771</v>
       </c>
       <c r="D32" t="s">
-        <v>695</v>
+        <v>771</v>
       </c>
       <c r="E32" t="s">
         <v>7</v>
@@ -9608,13 +10169,13 @@
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>696</v>
+        <v>772</v>
       </c>
       <c r="C33" t="s">
-        <v>697</v>
+        <v>773</v>
       </c>
       <c r="D33" t="s">
-        <v>697</v>
+        <v>773</v>
       </c>
       <c r="E33" t="s">
         <v>7</v>
@@ -9622,13 +10183,13 @@
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>698</v>
+        <v>774</v>
       </c>
       <c r="C34" t="s">
-        <v>699</v>
+        <v>775</v>
       </c>
       <c r="D34" t="s">
-        <v>699</v>
+        <v>775</v>
       </c>
       <c r="E34" t="s">
         <v>7</v>
@@ -9636,13 +10197,13 @@
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>700</v>
+        <v>776</v>
       </c>
       <c r="C35" t="s">
-        <v>701</v>
+        <v>777</v>
       </c>
       <c r="D35" t="s">
-        <v>701</v>
+        <v>777</v>
       </c>
       <c r="E35" t="s">
         <v>7</v>
@@ -9650,13 +10211,13 @@
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>702</v>
+        <v>778</v>
       </c>
       <c r="C36" t="s">
-        <v>703</v>
+        <v>779</v>
       </c>
       <c r="D36" t="s">
-        <v>703</v>
+        <v>779</v>
       </c>
       <c r="E36" t="s">
         <v>7</v>
@@ -9664,13 +10225,13 @@
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>704</v>
+        <v>780</v>
       </c>
       <c r="C37" t="s">
-        <v>705</v>
+        <v>781</v>
       </c>
       <c r="D37" t="s">
-        <v>705</v>
+        <v>781</v>
       </c>
       <c r="E37" t="s">
         <v>7</v>
@@ -9678,13 +10239,13 @@
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>706</v>
+        <v>782</v>
       </c>
       <c r="C38" t="s">
-        <v>707</v>
+        <v>783</v>
       </c>
       <c r="D38" t="s">
-        <v>707</v>
+        <v>783</v>
       </c>
       <c r="E38" t="s">
         <v>7</v>
@@ -9692,13 +10253,13 @@
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>708</v>
+        <v>784</v>
       </c>
       <c r="C39" t="s">
-        <v>709</v>
+        <v>785</v>
       </c>
       <c r="D39" t="s">
-        <v>709</v>
+        <v>785</v>
       </c>
       <c r="E39" t="s">
         <v>7</v>
@@ -9706,13 +10267,13 @@
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>710</v>
+        <v>786</v>
       </c>
       <c r="C40" t="s">
-        <v>711</v>
+        <v>787</v>
       </c>
       <c r="D40" t="s">
-        <v>711</v>
+        <v>787</v>
       </c>
       <c r="E40" t="s">
         <v>7</v>
@@ -9720,13 +10281,13 @@
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
-        <v>712</v>
+        <v>788</v>
       </c>
       <c r="C41" t="s">
-        <v>713</v>
+        <v>789</v>
       </c>
       <c r="D41" t="s">
-        <v>713</v>
+        <v>789</v>
       </c>
       <c r="E41" t="s">
         <v>7</v>
@@ -9734,13 +10295,13 @@
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>714</v>
+        <v>790</v>
       </c>
       <c r="C42" t="s">
-        <v>715</v>
+        <v>791</v>
       </c>
       <c r="D42" t="s">
-        <v>715</v>
+        <v>791</v>
       </c>
       <c r="E42" t="s">
         <v>7</v>
@@ -9748,13 +10309,13 @@
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>716</v>
+        <v>792</v>
       </c>
       <c r="C43" t="s">
-        <v>717</v>
+        <v>793</v>
       </c>
       <c r="D43" t="s">
-        <v>717</v>
+        <v>793</v>
       </c>
       <c r="E43" t="s">
         <v>7</v>
@@ -9762,13 +10323,13 @@
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
-        <v>718</v>
+        <v>794</v>
       </c>
       <c r="C44" t="s">
-        <v>719</v>
+        <v>795</v>
       </c>
       <c r="D44" t="s">
-        <v>719</v>
+        <v>795</v>
       </c>
       <c r="E44" t="s">
         <v>7</v>
@@ -9776,13 +10337,13 @@
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
-        <v>720</v>
+        <v>796</v>
       </c>
       <c r="C45" t="s">
-        <v>721</v>
+        <v>797</v>
       </c>
       <c r="D45" t="s">
-        <v>721</v>
+        <v>797</v>
       </c>
       <c r="E45" t="s">
         <v>7</v>
@@ -9790,13 +10351,13 @@
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
-        <v>722</v>
+        <v>798</v>
       </c>
       <c r="C46" t="s">
-        <v>723</v>
+        <v>799</v>
       </c>
       <c r="D46" t="s">
-        <v>723</v>
+        <v>799</v>
       </c>
       <c r="E46" t="s">
         <v>7</v>
@@ -9804,13 +10365,13 @@
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>724</v>
+        <v>800</v>
       </c>
       <c r="C47" t="s">
-        <v>725</v>
+        <v>801</v>
       </c>
       <c r="D47" t="s">
-        <v>725</v>
+        <v>801</v>
       </c>
       <c r="E47" t="s">
         <v>7</v>
@@ -9818,13 +10379,13 @@
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>726</v>
+        <v>802</v>
       </c>
       <c r="C48" t="s">
-        <v>727</v>
+        <v>803</v>
       </c>
       <c r="D48" t="s">
-        <v>727</v>
+        <v>803</v>
       </c>
       <c r="E48" t="s">
         <v>7</v>
@@ -9832,13 +10393,13 @@
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
-        <v>728</v>
+        <v>804</v>
       </c>
       <c r="C49" t="s">
-        <v>729</v>
+        <v>805</v>
       </c>
       <c r="D49" t="s">
-        <v>729</v>
+        <v>805</v>
       </c>
       <c r="E49" t="s">
         <v>7</v>
@@ -9849,8 +10410,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0450009B-38FA-4B4A-B923-CD0813EF619B}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D72714E-7E76-49AD-B482-493D7375AD97}">
   <dimension ref="B9:E98"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9875,13 +10436,13 @@
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>730</v>
+        <v>806</v>
       </c>
       <c r="C11" t="s">
-        <v>731</v>
+        <v>807</v>
       </c>
       <c r="D11" t="s">
-        <v>731</v>
+        <v>807</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -9889,13 +10450,13 @@
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>732</v>
+        <v>808</v>
       </c>
       <c r="C12" t="s">
-        <v>733</v>
+        <v>809</v>
       </c>
       <c r="D12" t="s">
-        <v>733</v>
+        <v>809</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -9903,13 +10464,13 @@
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>734</v>
+        <v>810</v>
       </c>
       <c r="C13" t="s">
-        <v>735</v>
+        <v>811</v>
       </c>
       <c r="D13" t="s">
-        <v>735</v>
+        <v>811</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -9917,13 +10478,13 @@
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>736</v>
+        <v>812</v>
       </c>
       <c r="C14" t="s">
-        <v>737</v>
+        <v>813</v>
       </c>
       <c r="D14" t="s">
-        <v>737</v>
+        <v>813</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -9931,13 +10492,13 @@
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>738</v>
+        <v>814</v>
       </c>
       <c r="C15" t="s">
-        <v>739</v>
+        <v>815</v>
       </c>
       <c r="D15" t="s">
-        <v>739</v>
+        <v>815</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -9945,13 +10506,13 @@
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>740</v>
+        <v>816</v>
       </c>
       <c r="C16" t="s">
-        <v>741</v>
+        <v>817</v>
       </c>
       <c r="D16" t="s">
-        <v>741</v>
+        <v>817</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -9959,13 +10520,13 @@
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>742</v>
+        <v>818</v>
       </c>
       <c r="C17" t="s">
-        <v>743</v>
+        <v>819</v>
       </c>
       <c r="D17" t="s">
-        <v>743</v>
+        <v>819</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -9973,13 +10534,13 @@
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>744</v>
+        <v>820</v>
       </c>
       <c r="C18" t="s">
-        <v>745</v>
+        <v>821</v>
       </c>
       <c r="D18" t="s">
-        <v>745</v>
+        <v>821</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
@@ -9987,13 +10548,13 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>746</v>
+        <v>822</v>
       </c>
       <c r="C19" t="s">
-        <v>747</v>
+        <v>823</v>
       </c>
       <c r="D19" t="s">
-        <v>747</v>
+        <v>823</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -10001,13 +10562,13 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>748</v>
+        <v>824</v>
       </c>
       <c r="C20" t="s">
-        <v>749</v>
+        <v>825</v>
       </c>
       <c r="D20" t="s">
-        <v>749</v>
+        <v>825</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
@@ -10015,13 +10576,13 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>750</v>
+        <v>826</v>
       </c>
       <c r="C21" t="s">
-        <v>751</v>
+        <v>827</v>
       </c>
       <c r="D21" t="s">
-        <v>751</v>
+        <v>827</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
@@ -10029,13 +10590,13 @@
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>752</v>
+        <v>828</v>
       </c>
       <c r="C22" t="s">
-        <v>753</v>
+        <v>829</v>
       </c>
       <c r="D22" t="s">
-        <v>753</v>
+        <v>829</v>
       </c>
       <c r="E22" t="s">
         <v>7</v>
@@ -10043,13 +10604,13 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>754</v>
+        <v>830</v>
       </c>
       <c r="C23" t="s">
-        <v>755</v>
+        <v>831</v>
       </c>
       <c r="D23" t="s">
-        <v>755</v>
+        <v>831</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
@@ -10057,13 +10618,13 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>756</v>
+        <v>832</v>
       </c>
       <c r="C24" t="s">
-        <v>757</v>
+        <v>833</v>
       </c>
       <c r="D24" t="s">
-        <v>757</v>
+        <v>833</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
@@ -10071,13 +10632,13 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>758</v>
+        <v>834</v>
       </c>
       <c r="C25" t="s">
-        <v>759</v>
+        <v>835</v>
       </c>
       <c r="D25" t="s">
-        <v>759</v>
+        <v>835</v>
       </c>
       <c r="E25" t="s">
         <v>7</v>
@@ -10085,13 +10646,13 @@
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>760</v>
+        <v>836</v>
       </c>
       <c r="C26" t="s">
-        <v>761</v>
+        <v>837</v>
       </c>
       <c r="D26" t="s">
-        <v>761</v>
+        <v>837</v>
       </c>
       <c r="E26" t="s">
         <v>7</v>
@@ -10099,13 +10660,13 @@
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>762</v>
+        <v>838</v>
       </c>
       <c r="C27" t="s">
-        <v>763</v>
+        <v>839</v>
       </c>
       <c r="D27" t="s">
-        <v>763</v>
+        <v>839</v>
       </c>
       <c r="E27" t="s">
         <v>7</v>
@@ -10113,13 +10674,13 @@
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>764</v>
+        <v>840</v>
       </c>
       <c r="C28" t="s">
-        <v>765</v>
+        <v>841</v>
       </c>
       <c r="D28" t="s">
-        <v>765</v>
+        <v>841</v>
       </c>
       <c r="E28" t="s">
         <v>7</v>
@@ -10127,13 +10688,13 @@
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>766</v>
+        <v>842</v>
       </c>
       <c r="C29" t="s">
-        <v>767</v>
+        <v>843</v>
       </c>
       <c r="D29" t="s">
-        <v>767</v>
+        <v>843</v>
       </c>
       <c r="E29" t="s">
         <v>7</v>
@@ -10141,13 +10702,13 @@
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>768</v>
+        <v>844</v>
       </c>
       <c r="C30" t="s">
-        <v>769</v>
+        <v>845</v>
       </c>
       <c r="D30" t="s">
-        <v>769</v>
+        <v>845</v>
       </c>
       <c r="E30" t="s">
         <v>7</v>
@@ -10155,13 +10716,13 @@
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>770</v>
+        <v>846</v>
       </c>
       <c r="C31" t="s">
-        <v>771</v>
+        <v>847</v>
       </c>
       <c r="D31" t="s">
-        <v>771</v>
+        <v>847</v>
       </c>
       <c r="E31" t="s">
         <v>7</v>
@@ -10169,13 +10730,13 @@
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>772</v>
+        <v>848</v>
       </c>
       <c r="C32" t="s">
-        <v>773</v>
+        <v>849</v>
       </c>
       <c r="D32" t="s">
-        <v>773</v>
+        <v>849</v>
       </c>
       <c r="E32" t="s">
         <v>7</v>
@@ -10183,13 +10744,13 @@
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>774</v>
+        <v>850</v>
       </c>
       <c r="C33" t="s">
-        <v>775</v>
+        <v>851</v>
       </c>
       <c r="D33" t="s">
-        <v>775</v>
+        <v>851</v>
       </c>
       <c r="E33" t="s">
         <v>7</v>
@@ -10197,13 +10758,13 @@
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>776</v>
+        <v>852</v>
       </c>
       <c r="C34" t="s">
-        <v>777</v>
+        <v>853</v>
       </c>
       <c r="D34" t="s">
-        <v>777</v>
+        <v>853</v>
       </c>
       <c r="E34" t="s">
         <v>7</v>
@@ -10211,13 +10772,13 @@
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>778</v>
+        <v>854</v>
       </c>
       <c r="C35" t="s">
-        <v>779</v>
+        <v>855</v>
       </c>
       <c r="D35" t="s">
-        <v>779</v>
+        <v>855</v>
       </c>
       <c r="E35" t="s">
         <v>7</v>
@@ -10225,13 +10786,13 @@
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>780</v>
+        <v>856</v>
       </c>
       <c r="C36" t="s">
-        <v>781</v>
+        <v>857</v>
       </c>
       <c r="D36" t="s">
-        <v>781</v>
+        <v>857</v>
       </c>
       <c r="E36" t="s">
         <v>7</v>
@@ -10239,13 +10800,13 @@
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>782</v>
+        <v>858</v>
       </c>
       <c r="C37" t="s">
-        <v>783</v>
+        <v>859</v>
       </c>
       <c r="D37" t="s">
-        <v>783</v>
+        <v>859</v>
       </c>
       <c r="E37" t="s">
         <v>7</v>
@@ -10253,13 +10814,13 @@
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>784</v>
+        <v>860</v>
       </c>
       <c r="C38" t="s">
-        <v>785</v>
+        <v>861</v>
       </c>
       <c r="D38" t="s">
-        <v>785</v>
+        <v>861</v>
       </c>
       <c r="E38" t="s">
         <v>7</v>
@@ -10267,13 +10828,13 @@
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>786</v>
+        <v>862</v>
       </c>
       <c r="C39" t="s">
-        <v>787</v>
+        <v>863</v>
       </c>
       <c r="D39" t="s">
-        <v>787</v>
+        <v>863</v>
       </c>
       <c r="E39" t="s">
         <v>7</v>
@@ -10281,13 +10842,13 @@
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>788</v>
+        <v>864</v>
       </c>
       <c r="C40" t="s">
-        <v>789</v>
+        <v>865</v>
       </c>
       <c r="D40" t="s">
-        <v>789</v>
+        <v>865</v>
       </c>
       <c r="E40" t="s">
         <v>7</v>
@@ -10295,13 +10856,13 @@
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
-        <v>790</v>
+        <v>866</v>
       </c>
       <c r="C41" t="s">
-        <v>791</v>
+        <v>867</v>
       </c>
       <c r="D41" t="s">
-        <v>791</v>
+        <v>867</v>
       </c>
       <c r="E41" t="s">
         <v>7</v>
@@ -10309,13 +10870,13 @@
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>792</v>
+        <v>868</v>
       </c>
       <c r="C42" t="s">
-        <v>793</v>
+        <v>869</v>
       </c>
       <c r="D42" t="s">
-        <v>793</v>
+        <v>869</v>
       </c>
       <c r="E42" t="s">
         <v>7</v>
@@ -10323,13 +10884,13 @@
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>794</v>
+        <v>870</v>
       </c>
       <c r="C43" t="s">
-        <v>795</v>
+        <v>871</v>
       </c>
       <c r="D43" t="s">
-        <v>795</v>
+        <v>871</v>
       </c>
       <c r="E43" t="s">
         <v>7</v>
@@ -10337,13 +10898,13 @@
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
-        <v>796</v>
+        <v>872</v>
       </c>
       <c r="C44" t="s">
-        <v>797</v>
+        <v>873</v>
       </c>
       <c r="D44" t="s">
-        <v>797</v>
+        <v>873</v>
       </c>
       <c r="E44" t="s">
         <v>7</v>
@@ -10351,13 +10912,13 @@
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
-        <v>798</v>
+        <v>874</v>
       </c>
       <c r="C45" t="s">
-        <v>799</v>
+        <v>875</v>
       </c>
       <c r="D45" t="s">
-        <v>799</v>
+        <v>875</v>
       </c>
       <c r="E45" t="s">
         <v>7</v>
@@ -10365,13 +10926,13 @@
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
-        <v>800</v>
+        <v>876</v>
       </c>
       <c r="C46" t="s">
-        <v>801</v>
+        <v>877</v>
       </c>
       <c r="D46" t="s">
-        <v>801</v>
+        <v>877</v>
       </c>
       <c r="E46" t="s">
         <v>7</v>
@@ -10379,13 +10940,13 @@
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>802</v>
+        <v>878</v>
       </c>
       <c r="C47" t="s">
-        <v>803</v>
+        <v>879</v>
       </c>
       <c r="D47" t="s">
-        <v>803</v>
+        <v>879</v>
       </c>
       <c r="E47" t="s">
         <v>7</v>
@@ -10393,13 +10954,13 @@
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>804</v>
+        <v>880</v>
       </c>
       <c r="C48" t="s">
-        <v>805</v>
+        <v>881</v>
       </c>
       <c r="D48" t="s">
-        <v>805</v>
+        <v>881</v>
       </c>
       <c r="E48" t="s">
         <v>7</v>
@@ -10407,13 +10968,13 @@
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
-        <v>806</v>
+        <v>882</v>
       </c>
       <c r="C49" t="s">
-        <v>807</v>
+        <v>883</v>
       </c>
       <c r="D49" t="s">
-        <v>807</v>
+        <v>883</v>
       </c>
       <c r="E49" t="s">
         <v>7</v>
@@ -10421,13 +10982,13 @@
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
-        <v>808</v>
+        <v>884</v>
       </c>
       <c r="C50" t="s">
-        <v>809</v>
+        <v>885</v>
       </c>
       <c r="D50" t="s">
-        <v>809</v>
+        <v>885</v>
       </c>
       <c r="E50" t="s">
         <v>7</v>
@@ -10435,13 +10996,13 @@
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
-        <v>810</v>
+        <v>886</v>
       </c>
       <c r="C51" t="s">
-        <v>811</v>
+        <v>887</v>
       </c>
       <c r="D51" t="s">
-        <v>811</v>
+        <v>887</v>
       </c>
       <c r="E51" t="s">
         <v>7</v>
@@ -10449,13 +11010,13 @@
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
-        <v>812</v>
+        <v>888</v>
       </c>
       <c r="C52" t="s">
-        <v>813</v>
+        <v>889</v>
       </c>
       <c r="D52" t="s">
-        <v>813</v>
+        <v>889</v>
       </c>
       <c r="E52" t="s">
         <v>7</v>
@@ -10463,13 +11024,13 @@
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
-        <v>814</v>
+        <v>890</v>
       </c>
       <c r="C53" t="s">
-        <v>815</v>
+        <v>891</v>
       </c>
       <c r="D53" t="s">
-        <v>815</v>
+        <v>891</v>
       </c>
       <c r="E53" t="s">
         <v>7</v>
@@ -10477,13 +11038,13 @@
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
-        <v>816</v>
+        <v>892</v>
       </c>
       <c r="C54" t="s">
-        <v>817</v>
+        <v>893</v>
       </c>
       <c r="D54" t="s">
-        <v>817</v>
+        <v>893</v>
       </c>
       <c r="E54" t="s">
         <v>7</v>
@@ -10491,13 +11052,13 @@
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
-        <v>818</v>
+        <v>894</v>
       </c>
       <c r="C55" t="s">
-        <v>819</v>
+        <v>895</v>
       </c>
       <c r="D55" t="s">
-        <v>819</v>
+        <v>895</v>
       </c>
       <c r="E55" t="s">
         <v>7</v>
@@ -10505,13 +11066,13 @@
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
-        <v>820</v>
+        <v>896</v>
       </c>
       <c r="C56" t="s">
-        <v>821</v>
+        <v>897</v>
       </c>
       <c r="D56" t="s">
-        <v>821</v>
+        <v>897</v>
       </c>
       <c r="E56" t="s">
         <v>7</v>
@@ -10519,13 +11080,13 @@
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>822</v>
+        <v>898</v>
       </c>
       <c r="C57" t="s">
-        <v>823</v>
+        <v>899</v>
       </c>
       <c r="D57" t="s">
-        <v>823</v>
+        <v>899</v>
       </c>
       <c r="E57" t="s">
         <v>7</v>
@@ -10533,13 +11094,13 @@
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>824</v>
+        <v>900</v>
       </c>
       <c r="C58" t="s">
-        <v>825</v>
+        <v>901</v>
       </c>
       <c r="D58" t="s">
-        <v>825</v>
+        <v>901</v>
       </c>
       <c r="E58" t="s">
         <v>7</v>
@@ -10547,13 +11108,13 @@
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
-        <v>826</v>
+        <v>902</v>
       </c>
       <c r="C59" t="s">
-        <v>827</v>
+        <v>903</v>
       </c>
       <c r="D59" t="s">
-        <v>827</v>
+        <v>903</v>
       </c>
       <c r="E59" t="s">
         <v>7</v>
@@ -10561,13 +11122,13 @@
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
-        <v>828</v>
+        <v>904</v>
       </c>
       <c r="C60" t="s">
-        <v>829</v>
+        <v>905</v>
       </c>
       <c r="D60" t="s">
-        <v>829</v>
+        <v>905</v>
       </c>
       <c r="E60" t="s">
         <v>7</v>
@@ -10575,13 +11136,13 @@
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
-        <v>830</v>
+        <v>906</v>
       </c>
       <c r="C61" t="s">
-        <v>831</v>
+        <v>907</v>
       </c>
       <c r="D61" t="s">
-        <v>831</v>
+        <v>907</v>
       </c>
       <c r="E61" t="s">
         <v>7</v>
@@ -10589,13 +11150,13 @@
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
-        <v>832</v>
+        <v>908</v>
       </c>
       <c r="C62" t="s">
-        <v>833</v>
+        <v>909</v>
       </c>
       <c r="D62" t="s">
-        <v>833</v>
+        <v>909</v>
       </c>
       <c r="E62" t="s">
         <v>7</v>
@@ -10603,13 +11164,13 @@
     </row>
     <row r="63" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
-        <v>834</v>
+        <v>910</v>
       </c>
       <c r="C63" t="s">
-        <v>835</v>
+        <v>911</v>
       </c>
       <c r="D63" t="s">
-        <v>835</v>
+        <v>911</v>
       </c>
       <c r="E63" t="s">
         <v>7</v>
@@ -10617,13 +11178,13 @@
     </row>
     <row r="64" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
-        <v>836</v>
+        <v>912</v>
       </c>
       <c r="C64" t="s">
-        <v>837</v>
+        <v>913</v>
       </c>
       <c r="D64" t="s">
-        <v>837</v>
+        <v>913</v>
       </c>
       <c r="E64" t="s">
         <v>7</v>
@@ -10631,13 +11192,13 @@
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
-        <v>838</v>
+        <v>914</v>
       </c>
       <c r="C65" t="s">
-        <v>839</v>
+        <v>915</v>
       </c>
       <c r="D65" t="s">
-        <v>839</v>
+        <v>915</v>
       </c>
       <c r="E65" t="s">
         <v>7</v>
@@ -10645,13 +11206,13 @@
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
-        <v>840</v>
+        <v>916</v>
       </c>
       <c r="C66" t="s">
-        <v>841</v>
+        <v>917</v>
       </c>
       <c r="D66" t="s">
-        <v>841</v>
+        <v>917</v>
       </c>
       <c r="E66" t="s">
         <v>7</v>
@@ -10659,13 +11220,13 @@
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
-        <v>842</v>
+        <v>918</v>
       </c>
       <c r="C67" t="s">
-        <v>843</v>
+        <v>919</v>
       </c>
       <c r="D67" t="s">
-        <v>843</v>
+        <v>919</v>
       </c>
       <c r="E67" t="s">
         <v>7</v>
@@ -10673,13 +11234,13 @@
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
-        <v>844</v>
+        <v>920</v>
       </c>
       <c r="C68" t="s">
-        <v>845</v>
+        <v>921</v>
       </c>
       <c r="D68" t="s">
-        <v>845</v>
+        <v>921</v>
       </c>
       <c r="E68" t="s">
         <v>7</v>
@@ -10687,13 +11248,13 @@
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
-        <v>846</v>
+        <v>922</v>
       </c>
       <c r="C69" t="s">
-        <v>847</v>
+        <v>923</v>
       </c>
       <c r="D69" t="s">
-        <v>847</v>
+        <v>923</v>
       </c>
       <c r="E69" t="s">
         <v>7</v>
@@ -10701,13 +11262,13 @@
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
-        <v>848</v>
+        <v>924</v>
       </c>
       <c r="C70" t="s">
-        <v>849</v>
+        <v>925</v>
       </c>
       <c r="D70" t="s">
-        <v>849</v>
+        <v>925</v>
       </c>
       <c r="E70" t="s">
         <v>7</v>
@@ -10715,13 +11276,13 @@
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
-        <v>850</v>
+        <v>926</v>
       </c>
       <c r="C71" t="s">
-        <v>851</v>
+        <v>927</v>
       </c>
       <c r="D71" t="s">
-        <v>851</v>
+        <v>927</v>
       </c>
       <c r="E71" t="s">
         <v>7</v>
@@ -10729,13 +11290,13 @@
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
-        <v>852</v>
+        <v>928</v>
       </c>
       <c r="C72" t="s">
-        <v>853</v>
+        <v>929</v>
       </c>
       <c r="D72" t="s">
-        <v>853</v>
+        <v>929</v>
       </c>
       <c r="E72" t="s">
         <v>7</v>
@@ -10743,13 +11304,13 @@
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
-        <v>854</v>
+        <v>930</v>
       </c>
       <c r="C73" t="s">
-        <v>855</v>
+        <v>931</v>
       </c>
       <c r="D73" t="s">
-        <v>855</v>
+        <v>931</v>
       </c>
       <c r="E73" t="s">
         <v>7</v>
@@ -10757,13 +11318,13 @@
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
-        <v>856</v>
+        <v>932</v>
       </c>
       <c r="C74" t="s">
-        <v>857</v>
+        <v>933</v>
       </c>
       <c r="D74" t="s">
-        <v>857</v>
+        <v>933</v>
       </c>
       <c r="E74" t="s">
         <v>7</v>
@@ -10771,13 +11332,13 @@
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B75" t="s">
-        <v>858</v>
+        <v>934</v>
       </c>
       <c r="C75" t="s">
-        <v>859</v>
+        <v>935</v>
       </c>
       <c r="D75" t="s">
-        <v>859</v>
+        <v>935</v>
       </c>
       <c r="E75" t="s">
         <v>7</v>
@@ -10785,13 +11346,13 @@
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B76" t="s">
-        <v>860</v>
+        <v>936</v>
       </c>
       <c r="C76" t="s">
-        <v>861</v>
+        <v>937</v>
       </c>
       <c r="D76" t="s">
-        <v>861</v>
+        <v>937</v>
       </c>
       <c r="E76" t="s">
         <v>7</v>
@@ -10799,13 +11360,13 @@
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
-        <v>862</v>
+        <v>938</v>
       </c>
       <c r="C77" t="s">
-        <v>863</v>
+        <v>939</v>
       </c>
       <c r="D77" t="s">
-        <v>863</v>
+        <v>939</v>
       </c>
       <c r="E77" t="s">
         <v>7</v>
@@ -10813,13 +11374,13 @@
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B78" t="s">
-        <v>864</v>
+        <v>940</v>
       </c>
       <c r="C78" t="s">
-        <v>865</v>
+        <v>941</v>
       </c>
       <c r="D78" t="s">
-        <v>865</v>
+        <v>941</v>
       </c>
       <c r="E78" t="s">
         <v>7</v>
@@ -10827,13 +11388,13 @@
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B79" t="s">
-        <v>866</v>
+        <v>942</v>
       </c>
       <c r="C79" t="s">
-        <v>867</v>
+        <v>943</v>
       </c>
       <c r="D79" t="s">
-        <v>867</v>
+        <v>943</v>
       </c>
       <c r="E79" t="s">
         <v>7</v>
@@ -10841,13 +11402,13 @@
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B80" t="s">
-        <v>868</v>
+        <v>944</v>
       </c>
       <c r="C80" t="s">
-        <v>869</v>
+        <v>945</v>
       </c>
       <c r="D80" t="s">
-        <v>869</v>
+        <v>945</v>
       </c>
       <c r="E80" t="s">
         <v>7</v>
@@ -10855,13 +11416,13 @@
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B81" t="s">
-        <v>870</v>
+        <v>946</v>
       </c>
       <c r="C81" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="D81" t="s">
-        <v>871</v>
+        <v>947</v>
       </c>
       <c r="E81" t="s">
         <v>7</v>
@@ -10869,13 +11430,13 @@
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B82" t="s">
-        <v>872</v>
+        <v>948</v>
       </c>
       <c r="C82" t="s">
-        <v>873</v>
+        <v>949</v>
       </c>
       <c r="D82" t="s">
-        <v>873</v>
+        <v>949</v>
       </c>
       <c r="E82" t="s">
         <v>7</v>
@@ -10883,13 +11444,13 @@
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B83" t="s">
-        <v>874</v>
+        <v>950</v>
       </c>
       <c r="C83" t="s">
-        <v>875</v>
+        <v>951</v>
       </c>
       <c r="D83" t="s">
-        <v>875</v>
+        <v>951</v>
       </c>
       <c r="E83" t="s">
         <v>7</v>
@@ -10897,13 +11458,13 @@
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B84" t="s">
-        <v>876</v>
+        <v>952</v>
       </c>
       <c r="C84" t="s">
-        <v>877</v>
+        <v>953</v>
       </c>
       <c r="D84" t="s">
-        <v>877</v>
+        <v>953</v>
       </c>
       <c r="E84" t="s">
         <v>7</v>
@@ -10911,13 +11472,13 @@
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B85" t="s">
-        <v>878</v>
+        <v>954</v>
       </c>
       <c r="C85" t="s">
-        <v>879</v>
+        <v>955</v>
       </c>
       <c r="D85" t="s">
-        <v>879</v>
+        <v>955</v>
       </c>
       <c r="E85" t="s">
         <v>7</v>
@@ -10925,13 +11486,13 @@
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B86" t="s">
-        <v>880</v>
+        <v>956</v>
       </c>
       <c r="C86" t="s">
-        <v>881</v>
+        <v>957</v>
       </c>
       <c r="D86" t="s">
-        <v>881</v>
+        <v>957</v>
       </c>
       <c r="E86" t="s">
         <v>7</v>
@@ -10939,13 +11500,13 @@
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B87" t="s">
-        <v>882</v>
+        <v>958</v>
       </c>
       <c r="C87" t="s">
-        <v>883</v>
+        <v>959</v>
       </c>
       <c r="D87" t="s">
-        <v>883</v>
+        <v>959</v>
       </c>
       <c r="E87" t="s">
         <v>7</v>
@@ -10953,13 +11514,13 @@
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B88" t="s">
-        <v>884</v>
+        <v>960</v>
       </c>
       <c r="C88" t="s">
-        <v>885</v>
+        <v>961</v>
       </c>
       <c r="D88" t="s">
-        <v>885</v>
+        <v>961</v>
       </c>
       <c r="E88" t="s">
         <v>7</v>
@@ -10967,13 +11528,13 @@
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B89" t="s">
-        <v>886</v>
+        <v>962</v>
       </c>
       <c r="C89" t="s">
-        <v>887</v>
+        <v>963</v>
       </c>
       <c r="D89" t="s">
-        <v>887</v>
+        <v>963</v>
       </c>
       <c r="E89" t="s">
         <v>7</v>
@@ -10981,13 +11542,13 @@
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B90" t="s">
-        <v>888</v>
+        <v>964</v>
       </c>
       <c r="C90" t="s">
-        <v>889</v>
+        <v>965</v>
       </c>
       <c r="D90" t="s">
-        <v>889</v>
+        <v>965</v>
       </c>
       <c r="E90" t="s">
         <v>7</v>
@@ -10995,13 +11556,13 @@
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B91" t="s">
-        <v>890</v>
+        <v>966</v>
       </c>
       <c r="C91" t="s">
-        <v>891</v>
+        <v>967</v>
       </c>
       <c r="D91" t="s">
-        <v>891</v>
+        <v>967</v>
       </c>
       <c r="E91" t="s">
         <v>7</v>
@@ -11009,13 +11570,13 @@
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B92" t="s">
-        <v>892</v>
+        <v>968</v>
       </c>
       <c r="C92" t="s">
-        <v>893</v>
+        <v>969</v>
       </c>
       <c r="D92" t="s">
-        <v>893</v>
+        <v>969</v>
       </c>
       <c r="E92" t="s">
         <v>7</v>
@@ -11023,13 +11584,13 @@
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B93" t="s">
-        <v>894</v>
+        <v>970</v>
       </c>
       <c r="C93" t="s">
-        <v>895</v>
+        <v>971</v>
       </c>
       <c r="D93" t="s">
-        <v>895</v>
+        <v>971</v>
       </c>
       <c r="E93" t="s">
         <v>7</v>
@@ -11037,13 +11598,13 @@
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B94" t="s">
-        <v>896</v>
+        <v>972</v>
       </c>
       <c r="C94" t="s">
-        <v>897</v>
+        <v>973</v>
       </c>
       <c r="D94" t="s">
-        <v>897</v>
+        <v>973</v>
       </c>
       <c r="E94" t="s">
         <v>7</v>
@@ -11051,13 +11612,13 @@
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B95" t="s">
-        <v>898</v>
+        <v>974</v>
       </c>
       <c r="C95" t="s">
-        <v>899</v>
+        <v>975</v>
       </c>
       <c r="D95" t="s">
-        <v>899</v>
+        <v>975</v>
       </c>
       <c r="E95" t="s">
         <v>7</v>
@@ -11065,13 +11626,13 @@
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B96" t="s">
-        <v>900</v>
+        <v>976</v>
       </c>
       <c r="C96" t="s">
-        <v>901</v>
+        <v>977</v>
       </c>
       <c r="D96" t="s">
-        <v>901</v>
+        <v>977</v>
       </c>
       <c r="E96" t="s">
         <v>7</v>
@@ -11079,13 +11640,13 @@
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B97" t="s">
-        <v>902</v>
+        <v>978</v>
       </c>
       <c r="C97" t="s">
-        <v>903</v>
+        <v>979</v>
       </c>
       <c r="D97" t="s">
-        <v>903</v>
+        <v>979</v>
       </c>
       <c r="E97" t="s">
         <v>7</v>
@@ -11093,13 +11654,13 @@
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B98" t="s">
-        <v>904</v>
+        <v>980</v>
       </c>
       <c r="C98" t="s">
-        <v>905</v>
+        <v>981</v>
       </c>
       <c r="D98" t="s">
-        <v>905</v>
+        <v>981</v>
       </c>
       <c r="E98" t="s">
         <v>7</v>
@@ -11110,8 +11671,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{410B152E-A4C3-47A2-AF79-6380E988887E}">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01AC0A71-167E-446A-BDAF-3A09560D725D}">
   <dimension ref="B9:E97"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11136,13 +11697,13 @@
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>906</v>
+        <v>982</v>
       </c>
       <c r="C11" t="s">
-        <v>907</v>
+        <v>983</v>
       </c>
       <c r="D11" t="s">
-        <v>907</v>
+        <v>983</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -11150,13 +11711,13 @@
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>908</v>
+        <v>984</v>
       </c>
       <c r="C12" t="s">
-        <v>909</v>
+        <v>985</v>
       </c>
       <c r="D12" t="s">
-        <v>909</v>
+        <v>985</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -11164,13 +11725,13 @@
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>910</v>
+        <v>986</v>
       </c>
       <c r="C13" t="s">
-        <v>911</v>
+        <v>987</v>
       </c>
       <c r="D13" t="s">
-        <v>911</v>
+        <v>987</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -11178,13 +11739,13 @@
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>912</v>
+        <v>988</v>
       </c>
       <c r="C14" t="s">
-        <v>913</v>
+        <v>989</v>
       </c>
       <c r="D14" t="s">
-        <v>913</v>
+        <v>989</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -11192,13 +11753,13 @@
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>914</v>
+        <v>990</v>
       </c>
       <c r="C15" t="s">
-        <v>915</v>
+        <v>991</v>
       </c>
       <c r="D15" t="s">
-        <v>915</v>
+        <v>991</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -11206,13 +11767,13 @@
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>916</v>
+        <v>992</v>
       </c>
       <c r="C16" t="s">
-        <v>917</v>
+        <v>993</v>
       </c>
       <c r="D16" t="s">
-        <v>917</v>
+        <v>993</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -11220,13 +11781,13 @@
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>918</v>
+        <v>994</v>
       </c>
       <c r="C17" t="s">
-        <v>919</v>
+        <v>995</v>
       </c>
       <c r="D17" t="s">
-        <v>919</v>
+        <v>995</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -11234,13 +11795,13 @@
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>920</v>
+        <v>996</v>
       </c>
       <c r="C18" t="s">
-        <v>921</v>
+        <v>997</v>
       </c>
       <c r="D18" t="s">
-        <v>921</v>
+        <v>997</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
@@ -11248,13 +11809,13 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>922</v>
+        <v>998</v>
       </c>
       <c r="C19" t="s">
-        <v>923</v>
+        <v>999</v>
       </c>
       <c r="D19" t="s">
-        <v>923</v>
+        <v>999</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -11262,13 +11823,13 @@
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>924</v>
+        <v>1000</v>
       </c>
       <c r="C20" t="s">
-        <v>925</v>
+        <v>1001</v>
       </c>
       <c r="D20" t="s">
-        <v>925</v>
+        <v>1001</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
@@ -11276,13 +11837,13 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>926</v>
+        <v>1002</v>
       </c>
       <c r="C21" t="s">
-        <v>927</v>
+        <v>1003</v>
       </c>
       <c r="D21" t="s">
-        <v>927</v>
+        <v>1003</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
@@ -11290,13 +11851,13 @@
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>928</v>
+        <v>1004</v>
       </c>
       <c r="C22" t="s">
-        <v>929</v>
+        <v>1005</v>
       </c>
       <c r="D22" t="s">
-        <v>929</v>
+        <v>1005</v>
       </c>
       <c r="E22" t="s">
         <v>7</v>
@@ -11304,13 +11865,13 @@
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>930</v>
+        <v>1006</v>
       </c>
       <c r="C23" t="s">
-        <v>931</v>
+        <v>1007</v>
       </c>
       <c r="D23" t="s">
-        <v>931</v>
+        <v>1007</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
@@ -11318,13 +11879,13 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>932</v>
+        <v>1008</v>
       </c>
       <c r="C24" t="s">
-        <v>933</v>
+        <v>1009</v>
       </c>
       <c r="D24" t="s">
-        <v>933</v>
+        <v>1009</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
@@ -11332,13 +11893,13 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>934</v>
+        <v>1010</v>
       </c>
       <c r="C25" t="s">
-        <v>935</v>
+        <v>1011</v>
       </c>
       <c r="D25" t="s">
-        <v>935</v>
+        <v>1011</v>
       </c>
       <c r="E25" t="s">
         <v>7</v>
@@ -11346,13 +11907,13 @@
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>936</v>
+        <v>1012</v>
       </c>
       <c r="C26" t="s">
-        <v>937</v>
+        <v>1013</v>
       </c>
       <c r="D26" t="s">
-        <v>937</v>
+        <v>1013</v>
       </c>
       <c r="E26" t="s">
         <v>7</v>
@@ -11360,13 +11921,13 @@
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>938</v>
+        <v>1014</v>
       </c>
       <c r="C27" t="s">
-        <v>939</v>
+        <v>1015</v>
       </c>
       <c r="D27" t="s">
-        <v>939</v>
+        <v>1015</v>
       </c>
       <c r="E27" t="s">
         <v>7</v>
@@ -11374,13 +11935,13 @@
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>940</v>
+        <v>1016</v>
       </c>
       <c r="C28" t="s">
-        <v>941</v>
+        <v>1017</v>
       </c>
       <c r="D28" t="s">
-        <v>941</v>
+        <v>1017</v>
       </c>
       <c r="E28" t="s">
         <v>7</v>
@@ -11388,13 +11949,13 @@
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>942</v>
+        <v>1018</v>
       </c>
       <c r="C29" t="s">
-        <v>943</v>
+        <v>1019</v>
       </c>
       <c r="D29" t="s">
-        <v>943</v>
+        <v>1019</v>
       </c>
       <c r="E29" t="s">
         <v>7</v>
@@ -11402,13 +11963,13 @@
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>944</v>
+        <v>1020</v>
       </c>
       <c r="C30" t="s">
-        <v>945</v>
+        <v>1021</v>
       </c>
       <c r="D30" t="s">
-        <v>945</v>
+        <v>1021</v>
       </c>
       <c r="E30" t="s">
         <v>7</v>
@@ -11416,13 +11977,13 @@
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>946</v>
+        <v>1022</v>
       </c>
       <c r="C31" t="s">
-        <v>947</v>
+        <v>1023</v>
       </c>
       <c r="D31" t="s">
-        <v>947</v>
+        <v>1023</v>
       </c>
       <c r="E31" t="s">
         <v>7</v>
@@ -11430,13 +11991,13 @@
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>948</v>
+        <v>1024</v>
       </c>
       <c r="C32" t="s">
-        <v>949</v>
+        <v>1025</v>
       </c>
       <c r="D32" t="s">
-        <v>949</v>
+        <v>1025</v>
       </c>
       <c r="E32" t="s">
         <v>7</v>
@@ -11444,13 +12005,13 @@
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>950</v>
+        <v>1026</v>
       </c>
       <c r="C33" t="s">
-        <v>951</v>
+        <v>1027</v>
       </c>
       <c r="D33" t="s">
-        <v>951</v>
+        <v>1027</v>
       </c>
       <c r="E33" t="s">
         <v>7</v>
@@ -11458,13 +12019,13 @@
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>952</v>
+        <v>1028</v>
       </c>
       <c r="C34" t="s">
-        <v>953</v>
+        <v>1029</v>
       </c>
       <c r="D34" t="s">
-        <v>953</v>
+        <v>1029</v>
       </c>
       <c r="E34" t="s">
         <v>7</v>
@@ -11472,13 +12033,13 @@
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>954</v>
+        <v>1030</v>
       </c>
       <c r="C35" t="s">
-        <v>955</v>
+        <v>1031</v>
       </c>
       <c r="D35" t="s">
-        <v>955</v>
+        <v>1031</v>
       </c>
       <c r="E35" t="s">
         <v>7</v>
@@ -11486,13 +12047,13 @@
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>956</v>
+        <v>1032</v>
       </c>
       <c r="C36" t="s">
-        <v>957</v>
+        <v>1033</v>
       </c>
       <c r="D36" t="s">
-        <v>957</v>
+        <v>1033</v>
       </c>
       <c r="E36" t="s">
         <v>7</v>
@@ -11500,13 +12061,13 @@
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>958</v>
+        <v>1034</v>
       </c>
       <c r="C37" t="s">
-        <v>959</v>
+        <v>1035</v>
       </c>
       <c r="D37" t="s">
-        <v>959</v>
+        <v>1035</v>
       </c>
       <c r="E37" t="s">
         <v>7</v>
@@ -11514,13 +12075,13 @@
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>960</v>
+        <v>1036</v>
       </c>
       <c r="C38" t="s">
-        <v>961</v>
+        <v>1037</v>
       </c>
       <c r="D38" t="s">
-        <v>961</v>
+        <v>1037</v>
       </c>
       <c r="E38" t="s">
         <v>7</v>
@@ -11528,13 +12089,13 @@
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>962</v>
+        <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>963</v>
+        <v>1039</v>
       </c>
       <c r="D39" t="s">
-        <v>963</v>
+        <v>1039</v>
       </c>
       <c r="E39" t="s">
         <v>7</v>
@@ -11542,13 +12103,13 @@
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>964</v>
+        <v>1040</v>
       </c>
       <c r="C40" t="s">
-        <v>965</v>
+        <v>1041</v>
       </c>
       <c r="D40" t="s">
-        <v>965</v>
+        <v>1041</v>
       </c>
       <c r="E40" t="s">
         <v>7</v>
@@ -11556,13 +12117,13 @@
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
-        <v>966</v>
+        <v>1042</v>
       </c>
       <c r="C41" t="s">
-        <v>967</v>
+        <v>1043</v>
       </c>
       <c r="D41" t="s">
-        <v>967</v>
+        <v>1043</v>
       </c>
       <c r="E41" t="s">
         <v>7</v>
@@ -11570,13 +12131,13 @@
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>968</v>
+        <v>1044</v>
       </c>
       <c r="C42" t="s">
-        <v>969</v>
+        <v>1045</v>
       </c>
       <c r="D42" t="s">
-        <v>969</v>
+        <v>1045</v>
       </c>
       <c r="E42" t="s">
         <v>7</v>
@@ -11584,13 +12145,13 @@
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>970</v>
+        <v>1046</v>
       </c>
       <c r="C43" t="s">
-        <v>971</v>
+        <v>1047</v>
       </c>
       <c r="D43" t="s">
-        <v>971</v>
+        <v>1047</v>
       </c>
       <c r="E43" t="s">
         <v>7</v>
@@ -11598,13 +12159,13 @@
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
-        <v>972</v>
+        <v>1048</v>
       </c>
       <c r="C44" t="s">
-        <v>973</v>
+        <v>1049</v>
       </c>
       <c r="D44" t="s">
-        <v>973</v>
+        <v>1049</v>
       </c>
       <c r="E44" t="s">
         <v>7</v>
@@ -11612,13 +12173,13 @@
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
-        <v>974</v>
+        <v>1050</v>
       </c>
       <c r="C45" t="s">
-        <v>975</v>
+        <v>1051</v>
       </c>
       <c r="D45" t="s">
-        <v>975</v>
+        <v>1051</v>
       </c>
       <c r="E45" t="s">
         <v>7</v>
@@ -11626,13 +12187,13 @@
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
-        <v>976</v>
+        <v>1052</v>
       </c>
       <c r="C46" t="s">
-        <v>977</v>
+        <v>1053</v>
       </c>
       <c r="D46" t="s">
-        <v>977</v>
+        <v>1053</v>
       </c>
       <c r="E46" t="s">
         <v>7</v>
@@ -11640,13 +12201,13 @@
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>978</v>
+        <v>1054</v>
       </c>
       <c r="C47" t="s">
-        <v>979</v>
+        <v>1055</v>
       </c>
       <c r="D47" t="s">
-        <v>979</v>
+        <v>1055</v>
       </c>
       <c r="E47" t="s">
         <v>7</v>
@@ -11654,13 +12215,13 @@
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>980</v>
+        <v>1056</v>
       </c>
       <c r="C48" t="s">
-        <v>981</v>
+        <v>1057</v>
       </c>
       <c r="D48" t="s">
-        <v>981</v>
+        <v>1057</v>
       </c>
       <c r="E48" t="s">
         <v>7</v>
@@ -11668,13 +12229,13 @@
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
-        <v>982</v>
+        <v>1058</v>
       </c>
       <c r="C49" t="s">
-        <v>983</v>
+        <v>1059</v>
       </c>
       <c r="D49" t="s">
-        <v>983</v>
+        <v>1059</v>
       </c>
       <c r="E49" t="s">
         <v>7</v>
@@ -11682,13 +12243,13 @@
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
-        <v>984</v>
+        <v>1060</v>
       </c>
       <c r="C50" t="s">
-        <v>985</v>
+        <v>1061</v>
       </c>
       <c r="D50" t="s">
-        <v>985</v>
+        <v>1061</v>
       </c>
       <c r="E50" t="s">
         <v>7</v>
@@ -11696,13 +12257,13 @@
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
-        <v>986</v>
+        <v>1062</v>
       </c>
       <c r="C51" t="s">
-        <v>987</v>
+        <v>1063</v>
       </c>
       <c r="D51" t="s">
-        <v>987</v>
+        <v>1063</v>
       </c>
       <c r="E51" t="s">
         <v>7</v>
@@ -11710,13 +12271,13 @@
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
-        <v>988</v>
+        <v>1064</v>
       </c>
       <c r="C52" t="s">
-        <v>989</v>
+        <v>1065</v>
       </c>
       <c r="D52" t="s">
-        <v>989</v>
+        <v>1065</v>
       </c>
       <c r="E52" t="s">
         <v>7</v>
@@ -11724,13 +12285,13 @@
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
-        <v>990</v>
+        <v>1066</v>
       </c>
       <c r="C53" t="s">
-        <v>991</v>
+        <v>1067</v>
       </c>
       <c r="D53" t="s">
-        <v>991</v>
+        <v>1067</v>
       </c>
       <c r="E53" t="s">
         <v>7</v>
@@ -11738,13 +12299,13 @@
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
-        <v>992</v>
+        <v>1068</v>
       </c>
       <c r="C54" t="s">
-        <v>993</v>
+        <v>1069</v>
       </c>
       <c r="D54" t="s">
-        <v>993</v>
+        <v>1069</v>
       </c>
       <c r="E54" t="s">
         <v>7</v>
@@ -11752,13 +12313,13 @@
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
-        <v>994</v>
+        <v>1070</v>
       </c>
       <c r="C55" t="s">
-        <v>995</v>
+        <v>1071</v>
       </c>
       <c r="D55" t="s">
-        <v>995</v>
+        <v>1071</v>
       </c>
       <c r="E55" t="s">
         <v>7</v>
@@ -11766,13 +12327,13 @@
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
-        <v>996</v>
+        <v>1072</v>
       </c>
       <c r="C56" t="s">
-        <v>997</v>
+        <v>1073</v>
       </c>
       <c r="D56" t="s">
-        <v>997</v>
+        <v>1073</v>
       </c>
       <c r="E56" t="s">
         <v>7</v>
@@ -11780,13 +12341,13 @@
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>998</v>
+        <v>1074</v>
       </c>
       <c r="C57" t="s">
-        <v>999</v>
+        <v>1075</v>
       </c>
       <c r="D57" t="s">
-        <v>999</v>
+        <v>1075</v>
       </c>
       <c r="E57" t="s">
         <v>7</v>
@@ -11794,13 +12355,13 @@
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>1000</v>
+        <v>1076</v>
       </c>
       <c r="C58" t="s">
-        <v>1001</v>
+        <v>1077</v>
       </c>
       <c r="D58" t="s">
-        <v>1001</v>
+        <v>1077</v>
       </c>
       <c r="E58" t="s">
         <v>7</v>
@@ -11808,13 +12369,13 @@
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
-        <v>1002</v>
+        <v>1078</v>
       </c>
       <c r="C59" t="s">
-        <v>1003</v>
+        <v>1079</v>
       </c>
       <c r="D59" t="s">
-        <v>1003</v>
+        <v>1079</v>
       </c>
       <c r="E59" t="s">
         <v>7</v>
@@ -11822,13 +12383,13 @@
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
-        <v>1004</v>
+        <v>1080</v>
       </c>
       <c r="C60" t="s">
-        <v>1005</v>
+        <v>1081</v>
       </c>
       <c r="D60" t="s">
-        <v>1005</v>
+        <v>1081</v>
       </c>
       <c r="E60" t="s">
         <v>7</v>
@@ -11836,13 +12397,13 @@
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
-        <v>1006</v>
+        <v>1082</v>
       </c>
       <c r="C61" t="s">
-        <v>1007</v>
+        <v>1083</v>
       </c>
       <c r="D61" t="s">
-        <v>1007</v>
+        <v>1083</v>
       </c>
       <c r="E61" t="s">
         <v>7</v>
@@ -11850,13 +12411,13 @@
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
-        <v>1008</v>
+        <v>1084</v>
       </c>
       <c r="C62" t="s">
-        <v>1009</v>
+        <v>1085</v>
       </c>
       <c r="D62" t="s">
-        <v>1009</v>
+        <v>1085</v>
       </c>
       <c r="E62" t="s">
         <v>7</v>
@@ -11864,13 +12425,13 @@
     </row>
     <row r="63" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
-        <v>1010</v>
+        <v>1086</v>
       </c>
       <c r="C63" t="s">
-        <v>1011</v>
+        <v>1087</v>
       </c>
       <c r="D63" t="s">
-        <v>1011</v>
+        <v>1087</v>
       </c>
       <c r="E63" t="s">
         <v>7</v>
@@ -11878,13 +12439,13 @@
     </row>
     <row r="64" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
-        <v>1012</v>
+        <v>1088</v>
       </c>
       <c r="C64" t="s">
-        <v>1013</v>
+        <v>1089</v>
       </c>
       <c r="D64" t="s">
-        <v>1013</v>
+        <v>1089</v>
       </c>
       <c r="E64" t="s">
         <v>7</v>
@@ -11892,13 +12453,13 @@
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
-        <v>1014</v>
+        <v>1090</v>
       </c>
       <c r="C65" t="s">
-        <v>1015</v>
+        <v>1091</v>
       </c>
       <c r="D65" t="s">
-        <v>1015</v>
+        <v>1091</v>
       </c>
       <c r="E65" t="s">
         <v>7</v>
@@ -11906,13 +12467,13 @@
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
-        <v>1016</v>
+        <v>1092</v>
       </c>
       <c r="C66" t="s">
-        <v>1017</v>
+        <v>1093</v>
       </c>
       <c r="D66" t="s">
-        <v>1017</v>
+        <v>1093</v>
       </c>
       <c r="E66" t="s">
         <v>7</v>
@@ -11920,13 +12481,13 @@
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
-        <v>1018</v>
+        <v>1094</v>
       </c>
       <c r="C67" t="s">
-        <v>1019</v>
+        <v>1095</v>
       </c>
       <c r="D67" t="s">
-        <v>1019</v>
+        <v>1095</v>
       </c>
       <c r="E67" t="s">
         <v>7</v>
@@ -11934,13 +12495,13 @@
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
-        <v>1020</v>
+        <v>1096</v>
       </c>
       <c r="C68" t="s">
-        <v>1021</v>
+        <v>1097</v>
       </c>
       <c r="D68" t="s">
-        <v>1021</v>
+        <v>1097</v>
       </c>
       <c r="E68" t="s">
         <v>7</v>
@@ -11948,13 +12509,13 @@
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
-        <v>1022</v>
+        <v>1098</v>
       </c>
       <c r="C69" t="s">
-        <v>1023</v>
+        <v>1099</v>
       </c>
       <c r="D69" t="s">
-        <v>1023</v>
+        <v>1099</v>
       </c>
       <c r="E69" t="s">
         <v>7</v>
@@ -11962,13 +12523,13 @@
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
-        <v>1024</v>
+        <v>1100</v>
       </c>
       <c r="C70" t="s">
-        <v>1025</v>
+        <v>1101</v>
       </c>
       <c r="D70" t="s">
-        <v>1025</v>
+        <v>1101</v>
       </c>
       <c r="E70" t="s">
         <v>7</v>
@@ -11976,13 +12537,13 @@
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
-        <v>1026</v>
+        <v>1102</v>
       </c>
       <c r="C71" t="s">
-        <v>1027</v>
+        <v>1103</v>
       </c>
       <c r="D71" t="s">
-        <v>1027</v>
+        <v>1103</v>
       </c>
       <c r="E71" t="s">
         <v>7</v>
@@ -11990,13 +12551,13 @@
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
-        <v>1028</v>
+        <v>1104</v>
       </c>
       <c r="C72" t="s">
-        <v>1029</v>
+        <v>1105</v>
       </c>
       <c r="D72" t="s">
-        <v>1029</v>
+        <v>1105</v>
       </c>
       <c r="E72" t="s">
         <v>7</v>
@@ -12004,13 +12565,13 @@
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
-        <v>1030</v>
+        <v>1106</v>
       </c>
       <c r="C73" t="s">
-        <v>1031</v>
+        <v>1107</v>
       </c>
       <c r="D73" t="s">
-        <v>1031</v>
+        <v>1107</v>
       </c>
       <c r="E73" t="s">
         <v>7</v>
@@ -12018,13 +12579,13 @@
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
-        <v>1032</v>
+        <v>1108</v>
       </c>
       <c r="C74" t="s">
-        <v>1033</v>
+        <v>1109</v>
       </c>
       <c r="D74" t="s">
-        <v>1033</v>
+        <v>1109</v>
       </c>
       <c r="E74" t="s">
         <v>7</v>
@@ -12032,13 +12593,13 @@
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B75" t="s">
-        <v>1034</v>
+        <v>1110</v>
       </c>
       <c r="C75" t="s">
-        <v>1035</v>
+        <v>1111</v>
       </c>
       <c r="D75" t="s">
-        <v>1035</v>
+        <v>1111</v>
       </c>
       <c r="E75" t="s">
         <v>7</v>
@@ -12046,13 +12607,13 @@
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B76" t="s">
-        <v>1036</v>
+        <v>1112</v>
       </c>
       <c r="C76" t="s">
-        <v>1037</v>
+        <v>1113</v>
       </c>
       <c r="D76" t="s">
-        <v>1037</v>
+        <v>1113</v>
       </c>
       <c r="E76" t="s">
         <v>7</v>
@@ -12060,13 +12621,13 @@
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
-        <v>1038</v>
+        <v>1114</v>
       </c>
       <c r="C77" t="s">
-        <v>1039</v>
+        <v>1115</v>
       </c>
       <c r="D77" t="s">
-        <v>1039</v>
+        <v>1115</v>
       </c>
       <c r="E77" t="s">
         <v>7</v>
@@ -12074,13 +12635,13 @@
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B78" t="s">
-        <v>1040</v>
+        <v>1116</v>
       </c>
       <c r="C78" t="s">
-        <v>1041</v>
+        <v>1117</v>
       </c>
       <c r="D78" t="s">
-        <v>1041</v>
+        <v>1117</v>
       </c>
       <c r="E78" t="s">
         <v>7</v>
@@ -12088,13 +12649,13 @@
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B79" t="s">
-        <v>1042</v>
+        <v>1118</v>
       </c>
       <c r="C79" t="s">
-        <v>1043</v>
+        <v>1119</v>
       </c>
       <c r="D79" t="s">
-        <v>1043</v>
+        <v>1119</v>
       </c>
       <c r="E79" t="s">
         <v>7</v>
@@ -12102,13 +12663,13 @@
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B80" t="s">
-        <v>1044</v>
+        <v>1120</v>
       </c>
       <c r="C80" t="s">
-        <v>1045</v>
+        <v>1121</v>
       </c>
       <c r="D80" t="s">
-        <v>1045</v>
+        <v>1121</v>
       </c>
       <c r="E80" t="s">
         <v>7</v>
@@ -12116,13 +12677,13 @@
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B81" t="s">
-        <v>1046</v>
+        <v>1122</v>
       </c>
       <c r="C81" t="s">
-        <v>1047</v>
+        <v>1123</v>
       </c>
       <c r="D81" t="s">
-        <v>1047</v>
+        <v>1123</v>
       </c>
       <c r="E81" t="s">
         <v>7</v>
@@ -12130,13 +12691,13 @@
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B82" t="s">
-        <v>1048</v>
+        <v>1124</v>
       </c>
       <c r="C82" t="s">
-        <v>1049</v>
+        <v>1125</v>
       </c>
       <c r="D82" t="s">
-        <v>1049</v>
+        <v>1125</v>
       </c>
       <c r="E82" t="s">
         <v>7</v>
@@ -12144,13 +12705,13 @@
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B83" t="s">
-        <v>1050</v>
+        <v>1126</v>
       </c>
       <c r="C83" t="s">
-        <v>1051</v>
+        <v>1127</v>
       </c>
       <c r="D83" t="s">
-        <v>1051</v>
+        <v>1127</v>
       </c>
       <c r="E83" t="s">
         <v>7</v>
@@ -12158,13 +12719,13 @@
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B84" t="s">
-        <v>1052</v>
+        <v>1128</v>
       </c>
       <c r="C84" t="s">
-        <v>1053</v>
+        <v>1129</v>
       </c>
       <c r="D84" t="s">
-        <v>1053</v>
+        <v>1129</v>
       </c>
       <c r="E84" t="s">
         <v>7</v>
@@ -12172,13 +12733,13 @@
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B85" t="s">
-        <v>1054</v>
+        <v>1130</v>
       </c>
       <c r="C85" t="s">
-        <v>1055</v>
+        <v>1131</v>
       </c>
       <c r="D85" t="s">
-        <v>1055</v>
+        <v>1131</v>
       </c>
       <c r="E85" t="s">
         <v>7</v>
@@ -12186,13 +12747,13 @@
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B86" t="s">
-        <v>1056</v>
+        <v>1132</v>
       </c>
       <c r="C86" t="s">
-        <v>1057</v>
+        <v>1133</v>
       </c>
       <c r="D86" t="s">
-        <v>1057</v>
+        <v>1133</v>
       </c>
       <c r="E86" t="s">
         <v>7</v>
@@ -12200,13 +12761,13 @@
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B87" t="s">
-        <v>1058</v>
+        <v>1134</v>
       </c>
       <c r="C87" t="s">
-        <v>1059</v>
+        <v>1135</v>
       </c>
       <c r="D87" t="s">
-        <v>1059</v>
+        <v>1135</v>
       </c>
       <c r="E87" t="s">
         <v>7</v>
@@ -12214,13 +12775,13 @@
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B88" t="s">
-        <v>1060</v>
+        <v>1136</v>
       </c>
       <c r="C88" t="s">
-        <v>1061</v>
+        <v>1137</v>
       </c>
       <c r="D88" t="s">
-        <v>1061</v>
+        <v>1137</v>
       </c>
       <c r="E88" t="s">
         <v>7</v>
@@ -12228,13 +12789,13 @@
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B89" t="s">
-        <v>1062</v>
+        <v>1138</v>
       </c>
       <c r="C89" t="s">
-        <v>1063</v>
+        <v>1139</v>
       </c>
       <c r="D89" t="s">
-        <v>1063</v>
+        <v>1139</v>
       </c>
       <c r="E89" t="s">
         <v>7</v>
@@ -12242,13 +12803,13 @@
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B90" t="s">
-        <v>1064</v>
+        <v>1140</v>
       </c>
       <c r="C90" t="s">
-        <v>1065</v>
+        <v>1141</v>
       </c>
       <c r="D90" t="s">
-        <v>1065</v>
+        <v>1141</v>
       </c>
       <c r="E90" t="s">
         <v>7</v>
@@ -12256,13 +12817,13 @@
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B91" t="s">
-        <v>1066</v>
+        <v>1142</v>
       </c>
       <c r="C91" t="s">
-        <v>1067</v>
+        <v>1143</v>
       </c>
       <c r="D91" t="s">
-        <v>1067</v>
+        <v>1143</v>
       </c>
       <c r="E91" t="s">
         <v>7</v>
@@ -12270,13 +12831,13 @@
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B92" t="s">
-        <v>1068</v>
+        <v>1144</v>
       </c>
       <c r="C92" t="s">
-        <v>1069</v>
+        <v>1145</v>
       </c>
       <c r="D92" t="s">
-        <v>1069</v>
+        <v>1145</v>
       </c>
       <c r="E92" t="s">
         <v>7</v>
@@ -12284,13 +12845,13 @@
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B93" t="s">
-        <v>1070</v>
+        <v>1146</v>
       </c>
       <c r="C93" t="s">
-        <v>1071</v>
+        <v>1147</v>
       </c>
       <c r="D93" t="s">
-        <v>1071</v>
+        <v>1147</v>
       </c>
       <c r="E93" t="s">
         <v>7</v>
@@ -12298,13 +12859,13 @@
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B94" t="s">
-        <v>1072</v>
+        <v>1148</v>
       </c>
       <c r="C94" t="s">
-        <v>1073</v>
+        <v>1149</v>
       </c>
       <c r="D94" t="s">
-        <v>1073</v>
+        <v>1149</v>
       </c>
       <c r="E94" t="s">
         <v>7</v>
@@ -12312,13 +12873,13 @@
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B95" t="s">
-        <v>1074</v>
+        <v>1150</v>
       </c>
       <c r="C95" t="s">
-        <v>1075</v>
+        <v>1151</v>
       </c>
       <c r="D95" t="s">
-        <v>1075</v>
+        <v>1151</v>
       </c>
       <c r="E95" t="s">
         <v>7</v>
@@ -12326,13 +12887,13 @@
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B96" t="s">
-        <v>1076</v>
+        <v>1152</v>
       </c>
       <c r="C96" t="s">
-        <v>1077</v>
+        <v>1153</v>
       </c>
       <c r="D96" t="s">
-        <v>1077</v>
+        <v>1153</v>
       </c>
       <c r="E96" t="s">
         <v>7</v>
@@ -12340,576 +12901,15 @@
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B97" t="s">
-        <v>1078</v>
+        <v>1154</v>
       </c>
       <c r="C97" t="s">
-        <v>1079</v>
+        <v>1155</v>
       </c>
       <c r="D97" t="s">
-        <v>1079</v>
+        <v>1155</v>
       </c>
       <c r="E97" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E14F65-9E8E-4A6E-9013-CF9F095B5772}">
-  <dimension ref="B9:E48"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B9" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B11" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1081</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B12" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1083</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1083</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B13" t="s">
-        <v>1084</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1085</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1085</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B14" t="s">
-        <v>1086</v>
-      </c>
-      <c r="C14" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1087</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B15" t="s">
-        <v>1088</v>
-      </c>
-      <c r="C15" t="s">
-        <v>1089</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1089</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B16" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C16" t="s">
-        <v>1091</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1091</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B17" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1093</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1093</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B18" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1095</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B19" t="s">
-        <v>1096</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1097</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1097</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B20" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1099</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1099</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B21" t="s">
-        <v>1100</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1101</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1101</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B22" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C22" t="s">
-        <v>1103</v>
-      </c>
-      <c r="D22" t="s">
-        <v>1103</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B23" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C23" t="s">
-        <v>1105</v>
-      </c>
-      <c r="D23" t="s">
-        <v>1105</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B24" t="s">
-        <v>1106</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1107</v>
-      </c>
-      <c r="D24" t="s">
-        <v>1107</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B25" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C25" t="s">
-        <v>1109</v>
-      </c>
-      <c r="D25" t="s">
-        <v>1109</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B26" t="s">
-        <v>1110</v>
-      </c>
-      <c r="C26" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D26" t="s">
-        <v>1111</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B27" t="s">
-        <v>1112</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1113</v>
-      </c>
-      <c r="D27" t="s">
-        <v>1113</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B28" t="s">
-        <v>1114</v>
-      </c>
-      <c r="C28" t="s">
-        <v>1115</v>
-      </c>
-      <c r="D28" t="s">
-        <v>1115</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B29" t="s">
-        <v>1116</v>
-      </c>
-      <c r="C29" t="s">
-        <v>1117</v>
-      </c>
-      <c r="D29" t="s">
-        <v>1117</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B30" t="s">
-        <v>1118</v>
-      </c>
-      <c r="C30" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D30" t="s">
-        <v>1119</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B31" t="s">
-        <v>1120</v>
-      </c>
-      <c r="C31" t="s">
-        <v>1121</v>
-      </c>
-      <c r="D31" t="s">
-        <v>1121</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B32" t="s">
-        <v>1122</v>
-      </c>
-      <c r="C32" t="s">
-        <v>1123</v>
-      </c>
-      <c r="D32" t="s">
-        <v>1123</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B33" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C33" t="s">
-        <v>1125</v>
-      </c>
-      <c r="D33" t="s">
-        <v>1125</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B34" t="s">
-        <v>1126</v>
-      </c>
-      <c r="C34" t="s">
-        <v>1127</v>
-      </c>
-      <c r="D34" t="s">
-        <v>1127</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B35" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1129</v>
-      </c>
-      <c r="D35" t="s">
-        <v>1129</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B36" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C36" t="s">
-        <v>1131</v>
-      </c>
-      <c r="D36" t="s">
-        <v>1131</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B37" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C37" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D37" t="s">
-        <v>1133</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B38" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C38" t="s">
-        <v>1135</v>
-      </c>
-      <c r="D38" t="s">
-        <v>1135</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B39" t="s">
-        <v>1136</v>
-      </c>
-      <c r="C39" t="s">
-        <v>1137</v>
-      </c>
-      <c r="D39" t="s">
-        <v>1137</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B40" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C40" t="s">
-        <v>1139</v>
-      </c>
-      <c r="D40" t="s">
-        <v>1139</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B41" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C41" t="s">
-        <v>1141</v>
-      </c>
-      <c r="D41" t="s">
-        <v>1141</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B42" t="s">
-        <v>1142</v>
-      </c>
-      <c r="C42" t="s">
-        <v>1143</v>
-      </c>
-      <c r="D42" t="s">
-        <v>1143</v>
-      </c>
-      <c r="E42" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B43" t="s">
-        <v>1144</v>
-      </c>
-      <c r="C43" t="s">
-        <v>1145</v>
-      </c>
-      <c r="D43" t="s">
-        <v>1145</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B44" t="s">
-        <v>1146</v>
-      </c>
-      <c r="C44" t="s">
-        <v>1147</v>
-      </c>
-      <c r="D44" t="s">
-        <v>1147</v>
-      </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B45" t="s">
-        <v>1148</v>
-      </c>
-      <c r="C45" t="s">
-        <v>1149</v>
-      </c>
-      <c r="D45" t="s">
-        <v>1149</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B46" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C46" t="s">
-        <v>1151</v>
-      </c>
-      <c r="D46" t="s">
-        <v>1151</v>
-      </c>
-      <c r="E46" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B47" t="s">
-        <v>1152</v>
-      </c>
-      <c r="C47" t="s">
-        <v>1153</v>
-      </c>
-      <c r="D47" t="s">
-        <v>1153</v>
-      </c>
-      <c r="E47" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B48" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C48" t="s">
-        <v>1155</v>
-      </c>
-      <c r="D48" t="s">
-        <v>1155</v>
-      </c>
-      <c r="E48" t="s">
         <v>7</v>
       </c>
     </row>
@@ -12919,7 +12919,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92AF78F1-D388-4A5F-B49D-2FB1EF9C24E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39E2A2EA-A1AD-472F-8F85-FD824B4FCB08}">
   <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
